--- a/output/yearly_surface_area_iteration_53_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_53_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497617673163</v>
+        <v>10.84497629824495</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907140013104</v>
+        <v>37.78907182354144</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.170284321191204</v>
+        <v>5.908157684157304</v>
       </c>
       <c r="C2" t="n">
-        <v>12.98066814555133</v>
+        <v>5.701990666265475</v>
       </c>
       <c r="D2" t="n">
-        <v>17.4220947595639</v>
+        <v>23.04554560948963</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.44489594093983</v>
+        <v>18.6532063806894</v>
       </c>
       <c r="C3" t="n">
-        <v>31.79880814055419</v>
+        <v>30.37036523087508</v>
       </c>
       <c r="D3" t="n">
-        <v>59.82770509680063</v>
+        <v>62.4047928204485</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.9210278819663</v>
+        <v>36.1950743601714</v>
       </c>
       <c r="C4" t="n">
-        <v>73.4239290529147</v>
+        <v>97.66033462765571</v>
       </c>
       <c r="D4" t="n">
-        <v>81.28576466852316</v>
+        <v>88.82853228025141</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.84886157793756</v>
+        <v>45.18493808795945</v>
       </c>
       <c r="C5" t="n">
-        <v>86.61469120717486</v>
+        <v>157.7423123798563</v>
       </c>
       <c r="D5" t="n">
-        <v>61.45740628585034</v>
+        <v>74.68645660057611</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.35482149852316</v>
+        <v>42.02272873258048</v>
       </c>
       <c r="C6" t="n">
-        <v>87.82911311732816</v>
+        <v>158.0682526176662</v>
       </c>
       <c r="D6" t="n">
-        <v>45.80638438474769</v>
+        <v>53.13218575383738</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>37.24947139453248</v>
+        <v>28.26647990067416</v>
       </c>
       <c r="C7" t="n">
-        <v>91.14742035768236</v>
+        <v>123.186756685777</v>
       </c>
       <c r="D7" t="n">
-        <v>38.80652325346792</v>
+        <v>40.96244121199391</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19.27661617288612</v>
+        <v>14.43659999094934</v>
       </c>
       <c r="C8" t="n">
-        <v>64.58918146239766</v>
+        <v>74.43611093599316</v>
       </c>
       <c r="D8" t="n">
-        <v>36.46701847424777</v>
+        <v>36.30012136452581</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>7.321874378272709</v>
       </c>
       <c r="C9" t="n">
-        <v>38.71718421238145</v>
+        <v>40.71405904281946</v>
       </c>
       <c r="D9" t="n">
-        <v>33.9468721174462</v>
+        <v>33.83593462686631</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.694136684631501</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>30.60598467989432</v>
+        <v>30.46363126277853</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.852984190737</v>
+        <v>28.60910984945629</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.77167905773377</v>
+        <v>27.33774657245668</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.49763257952867</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>26.01631416254048</v>
+        <v>24.97566159603886</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>32.26022956155019</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>23.04652735719387</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>18.59921025695582</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1007,7 +1007,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1021,7 +1021,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.699671286910314</v>
+        <v>7.655201123592103</v>
       </c>
       <c r="C21" t="n">
-        <v>95.28343217551514</v>
+        <v>92.81931362355425</v>
       </c>
       <c r="D21" t="n">
-        <v>8.662130197774102</v>
+        <v>7.655201123592103</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.308530821040756</v>
+        <v>6.180101798233672</v>
       </c>
       <c r="C2" t="n">
-        <v>11.03680769114264</v>
+        <v>7.712609964562943</v>
       </c>
       <c r="D2" t="n">
-        <v>16.41187637189393</v>
+        <v>19.00172681569702</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.7148765596077</v>
+        <v>18.98700060013331</v>
       </c>
       <c r="C3" t="n">
-        <v>41.43466185773664</v>
+        <v>26.10467145592269</v>
       </c>
       <c r="D3" t="n">
-        <v>59.51354583144164</v>
+        <v>65.07023783747859</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.58545009356314</v>
+        <v>35.64627739349744</v>
       </c>
       <c r="C4" t="n">
-        <v>76.4231682893887</v>
+        <v>87.00346329805657</v>
       </c>
       <c r="D4" t="n">
-        <v>90.14309245623788</v>
+        <v>96.54997797415255</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>58.6839690213531</v>
+        <v>48.81740459367266</v>
       </c>
       <c r="C5" t="n">
-        <v>109.6366748717626</v>
+        <v>166.209886328985</v>
       </c>
       <c r="D5" t="n">
-        <v>75.05461198966867</v>
+        <v>87.17919613711678</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>61.46427851978007</v>
+        <v>50.15356321915257</v>
       </c>
       <c r="C6" t="n">
-        <v>111.8996033300515</v>
+        <v>200.0507296943726</v>
       </c>
       <c r="D6" t="n">
-        <v>53.17243740971151</v>
+        <v>61.86679507852126</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>47.9691745772034</v>
+        <v>37.72856427420492</v>
       </c>
       <c r="C7" t="n">
-        <v>108.035444366136</v>
+        <v>169.1197865243725</v>
       </c>
       <c r="D7" t="n">
-        <v>42.99858595060179</v>
+        <v>46.11268966847268</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>29.12354564648163</v>
+        <v>21.61317570899353</v>
       </c>
       <c r="C8" t="n">
-        <v>92.04375601165971</v>
+        <v>114.407968714402</v>
       </c>
       <c r="D8" t="n">
-        <v>38.30288668118931</v>
+        <v>38.38633523605029</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.86718632248619</v>
+        <v>10.42812411450962</v>
       </c>
       <c r="C9" t="n">
-        <v>58.13124506386212</v>
+        <v>63.12343213995715</v>
       </c>
       <c r="D9" t="n">
-        <v>35.72187196672443</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.975317438673588</v>
+        <v>6.121196935978863</v>
       </c>
       <c r="C10" t="n">
         <v>38.43542262126263</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>32.69612554223576</v>
+        <v>31.98534020436108</v>
       </c>
       <c r="D11" t="n">
-        <v>37.13853390395258</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -1234,7 +1234,7 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>31.02617269731195</v>
+        <v>29.72437524148068</v>
       </c>
       <c r="D12" t="n">
         <v>34.71459882216721</v>
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>28.35778243716912</v>
+        <v>27.57729301229291</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>26.11939767148639</v>
+        <v>24.89024954576939</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>19.83915760741954</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1318,7 +1318,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1332,7 +1332,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.884732905680231</v>
+        <v>7.825187457957212</v>
       </c>
       <c r="C21" t="n">
-        <v>104.4727110002631</v>
+        <v>100.7492885211991</v>
       </c>
       <c r="D21" t="n">
-        <v>9.855916132100289</v>
+        <v>8.803335890201865</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.082148011987242</v>
+        <v>6.731844008020379</v>
       </c>
       <c r="C2" t="n">
-        <v>15.68243782763855</v>
+        <v>13.33802430989717</v>
       </c>
       <c r="D2" t="n">
-        <v>19.18433188868692</v>
+        <v>19.14800722362979</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.72393327312417</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="C3" t="n">
-        <v>41.82736093943536</v>
+        <v>27.5478405811655</v>
       </c>
       <c r="D3" t="n">
-        <v>58.49252821902496</v>
+        <v>64.49591543049421</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.3347035183527</v>
+        <v>34.88051418418493</v>
       </c>
       <c r="C4" t="n">
-        <v>88.95615948180348</v>
+        <v>76.44869372969913</v>
       </c>
       <c r="D4" t="n">
-        <v>97.31574118346508</v>
+        <v>104.0672201455704</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>59.96024103687396</v>
+        <v>50.19185137961819</v>
       </c>
       <c r="C5" t="n">
-        <v>122.4239387195773</v>
+        <v>161.595672119025</v>
       </c>
       <c r="D5" t="n">
-        <v>86.19744843286996</v>
+        <v>96.92304210176638</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>68.91083485649213</v>
+        <v>56.19131160027045</v>
       </c>
       <c r="C6" t="n">
-        <v>139.5524909155714</v>
+        <v>226.858332506536</v>
       </c>
       <c r="D6" t="n">
-        <v>62.51082157250717</v>
+        <v>71.92970904705108</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>58.80865097979244</v>
+        <v>46.77144237802229</v>
       </c>
       <c r="C7" t="n">
-        <v>130.9720159804542</v>
+        <v>216.4900950019854</v>
       </c>
       <c r="D7" t="n">
-        <v>47.07087542781757</v>
+        <v>51.02339168511523</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>38.97047512007713</v>
+        <v>28.95664853675967</v>
       </c>
       <c r="C8" t="n">
-        <v>114.574865824124</v>
+        <v>158.3853571261379</v>
       </c>
       <c r="D8" t="n">
-        <v>40.80634332701867</v>
+        <v>41.22358610132356</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20.63437324785945</v>
+        <v>14.75468624712531</v>
       </c>
       <c r="C9" t="n">
-        <v>83.20311793491715</v>
+        <v>95.29530440812512</v>
       </c>
       <c r="D9" t="n">
-        <v>36.94218436310322</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>51.38958357879929</v>
+        <v>52.52841091572559</v>
       </c>
       <c r="D10" t="n">
-        <v>36.30012136452581</v>
+        <v>35.44600086183109</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.508586368528851</v>
+        <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
-        <v>38.20471191076462</v>
+        <v>36.96083756948391</v>
       </c>
       <c r="D11" t="n">
-        <v>37.13853390395258</v>
+        <v>36.96083756948391</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>33.62976760897449</v>
+        <v>32.54493639578176</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -1559,7 +1559,7 @@
         <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>30.95941385342317</v>
+        <v>29.65859814529614</v>
       </c>
       <c r="D13" t="n">
         <v>33.30088212805181</v>
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>28.27040689149115</v>
+        <v>26.73397173434489</v>
       </c>
       <c r="D14" t="n">
-        <v>31.65056423721292</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>25.083653843506</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>22.7323680918349</v>
+        <v>21.49242074137117</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1629,7 +1629,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>19.25796296650543</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.054096604261526</v>
+        <v>7.979196664672824</v>
       </c>
       <c r="C21" t="n">
-        <v>112.7573524596613</v>
+        <v>107.7191549730831</v>
       </c>
       <c r="D21" t="n">
-        <v>11.0743828308596</v>
+        <v>9.97399583084103</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.287914119251573</v>
+        <v>6.278276568658352</v>
       </c>
       <c r="C2" t="n">
-        <v>10.53807985738526</v>
+        <v>9.282424543653592</v>
       </c>
       <c r="D2" t="n">
-        <v>15.79632056133118</v>
+        <v>15.93671048303847</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>28.04853191033137</v>
+        <v>23.39995653072273</v>
       </c>
       <c r="C3" t="n">
-        <v>63.98540662428587</v>
+        <v>46.08323723734528</v>
       </c>
       <c r="D3" t="n">
-        <v>65.04078540635119</v>
+        <v>71.1128949571177</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.80545939030566</v>
+        <v>24.10877837318892</v>
       </c>
       <c r="C4" t="n">
-        <v>110.6400210255028</v>
+        <v>121.0288752318425</v>
       </c>
       <c r="D4" t="n">
-        <v>95.00568883537234</v>
+        <v>102.7654226897391</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.80357801035519</v>
+        <v>31.63681976935347</v>
       </c>
       <c r="C5" t="n">
-        <v>83.37492378316038</v>
+        <v>135.5548142638784</v>
       </c>
       <c r="D5" t="n">
-        <v>61.33468782281949</v>
+        <v>69.01686360855078</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.50825187782615</v>
+        <v>29.02144388523996</v>
       </c>
       <c r="C6" t="n">
-        <v>86.25929853823752</v>
+        <v>142.5713651061303</v>
       </c>
       <c r="D6" t="n">
-        <v>30.99377502307181</v>
+        <v>33.56988099901544</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.81112889235289</v>
+        <v>19.16371518689774</v>
       </c>
       <c r="C7" t="n">
-        <v>80.54749039492954</v>
+        <v>111.3890945238431</v>
       </c>
       <c r="D7" t="n">
-        <v>28.68568617038755</v>
+        <v>28.98511922018283</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.26970288122739</v>
+        <v>10.18072369303942</v>
       </c>
       <c r="C8" t="n">
-        <v>61.33468782281948</v>
+        <v>70.18023463808323</v>
       </c>
       <c r="D8" t="n">
-        <v>27.20422888467911</v>
+        <v>26.8704346652352</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.767186925373262</v>
+        <v>5.324999547834698</v>
       </c>
       <c r="C9" t="n">
-        <v>39.160934174701</v>
+        <v>40.04843409934012</v>
       </c>
       <c r="D9" t="n">
-        <v>27.62343515439249</v>
+        <v>27.06874770149305</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.98589567924205</v>
+        <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>28.89774367450487</v>
       </c>
       <c r="D10" t="n">
-        <v>29.04009709162065</v>
+        <v>28.89774367450487</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>28.43141351498762</v>
+        <v>27.8983245115816</v>
       </c>
     </row>
     <row r="12">
@@ -1856,7 +1856,7 @@
         <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
         <v>27.12078032981814</v>
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>22.11386703815941</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.89551813718911</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>23.66110142005238</v>
+        <v>24.58296251434014</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>22.21695054710532</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>16.11931555602838</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>20.66578917439536</v>
       </c>
     </row>
     <row r="17">
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
         <v>17.9443845382232</v>
@@ -1940,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.58662746324986</v>
+        <v>15.51652246562084</v>
       </c>
       <c r="D18" t="n">
         <v>13.9113649691773</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>75.31968386981528</v>
+        <v>72.62969516017901</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>6.724971774090649</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.14632146566178</v>
+        <v>3.852377991464484</v>
       </c>
       <c r="C2" t="n">
-        <v>5.075635630956009</v>
+        <v>4.76442160870977</v>
       </c>
       <c r="D2" t="n">
-        <v>10.89347252632261</v>
+        <v>11.87522023056942</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>29.12354564648163</v>
+        <v>23.14961086613979</v>
       </c>
       <c r="C3" t="n">
-        <v>53.24508673982577</v>
+        <v>42.00898426472102</v>
       </c>
       <c r="D3" t="n">
-        <v>63.19019098384595</v>
+        <v>68.86469271439252</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.89626320518188</v>
+        <v>32.71085175779947</v>
       </c>
       <c r="C4" t="n">
-        <v>137.7352759150105</v>
+        <v>122.6114525310884</v>
       </c>
       <c r="D4" t="n">
-        <v>105.3179667207808</v>
+        <v>112.4523272875424</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.09872421643498</v>
+        <v>35.19565519724816</v>
       </c>
       <c r="C5" t="n">
-        <v>140.2917469368692</v>
+        <v>176.1746255270901</v>
       </c>
       <c r="D5" t="n">
-        <v>75.79092276785377</v>
+        <v>84.94572010995527</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.71329827929349</v>
+        <v>33.97239755775664</v>
       </c>
       <c r="C6" t="n">
-        <v>109.4040006658561</v>
+        <v>178.0733255871035</v>
       </c>
       <c r="D6" t="n">
-        <v>38.19882142453915</v>
+        <v>41.0164373357275</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.3139636433765</v>
+        <v>17.90609637775757</v>
       </c>
       <c r="C7" t="n">
-        <v>99.89086541170445</v>
+        <v>145.7041220303819</v>
       </c>
       <c r="D7" t="n">
-        <v>31.26081039862693</v>
+        <v>31.56024344842221</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.68279768053704</v>
+        <v>8.428304040958867</v>
       </c>
       <c r="C8" t="n">
-        <v>79.44302422765189</v>
+        <v>94.38031554776711</v>
       </c>
       <c r="D8" t="n">
-        <v>28.37250865273282</v>
+        <v>27.62147165898401</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>4.326562132615692</v>
       </c>
       <c r="C9" t="n">
-        <v>45.04062117543515</v>
+        <v>43.93124626963626</v>
       </c>
       <c r="D9" t="n">
-        <v>28.6218725696115</v>
+        <v>28.39999758845172</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>32.74128593663113</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>29.60951076008381</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>30.03068052520567</v>
+        <v>28.78680618392497</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.14219885286231</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>21.69662426385451</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>27.98864530037232</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>17.17076734727672</v>
+        <v>16.3902779224005</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.67163860289184</v>
+        <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>18.4372218857551</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>13.22610507161303</v>
       </c>
       <c r="D16" t="n">
         <v>15.29268398905256</v>
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.16661937228147</v>
+        <v>13.22217808079604</v>
       </c>
       <c r="D17" t="n">
         <v>11.8055161435679</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.9113649691773</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>65.59743635465912</v>
+        <v>63.19019098384595</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>5.416302084329653</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.892449720889356</v>
+        <v>4.285328729037327</v>
       </c>
       <c r="C2" t="n">
-        <v>5.44477276775281</v>
+        <v>10.5115726693706</v>
       </c>
       <c r="D2" t="n">
-        <v>11.34016773175491</v>
+        <v>11.13989120008856</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.24287689804324</v>
+        <v>18.14760631300229</v>
       </c>
       <c r="C3" t="n">
-        <v>35.09257168830224</v>
+        <v>29.69295931494478</v>
       </c>
       <c r="D3" t="n">
-        <v>58.19309516922969</v>
+        <v>62.94475405778425</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>47.82191242156638</v>
+        <v>37.79041437957247</v>
       </c>
       <c r="C4" t="n">
-        <v>135.2082573242792</v>
+        <v>113.6264975418216</v>
       </c>
       <c r="D4" t="n">
-        <v>110.7293600665893</v>
+        <v>119.892993138029</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.97724954301564</v>
+        <v>41.50338419703392</v>
       </c>
       <c r="C5" t="n">
-        <v>198.5093857987051</v>
+        <v>201.6509784522949</v>
       </c>
       <c r="D5" t="n">
-        <v>94.14960483726912</v>
+        <v>102.5190040159732</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.55607977789376</v>
+        <v>40.29190752999335</v>
       </c>
       <c r="C6" t="n">
-        <v>162.7776963549382</v>
+        <v>224.2822265305924</v>
       </c>
       <c r="D6" t="n">
-        <v>50.87809302488671</v>
+        <v>54.6214970211798</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>35.75230614555609</v>
+        <v>26.35010838198439</v>
       </c>
       <c r="C7" t="n">
-        <v>128.516664972133</v>
+        <v>197.2664932051286</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17.10695374650067</v>
+        <v>12.43383467428585</v>
       </c>
       <c r="C8" t="n">
-        <v>104.7279363505285</v>
+        <v>137.8570126303371</v>
       </c>
       <c r="D8" t="n">
-        <v>29.95803119509142</v>
+        <v>29.37389131106456</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.432811868852599</v>
+        <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>69.0031191406913</v>
+        <v>73.88436872620643</v>
       </c>
       <c r="D9" t="n">
-        <v>29.39843500367073</v>
+        <v>29.28749751309084</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.847068342315751</v>
+        <v>2.562361508084175</v>
       </c>
       <c r="C10" t="n">
-        <v>41.56719779780995</v>
+        <v>40.28601704376787</v>
       </c>
       <c r="D10" t="n">
-        <v>30.7483380970101</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>34.29539255245382</v>
+        <v>32.34073287329842</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>26.03594911662541</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>29.07347651356504</v>
+        <v>28.63954402828795</v>
       </c>
     </row>
     <row r="13">
@@ -2492,7 +2492,7 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.77239876353076</v>
+        <v>18.47158305540374</v>
       </c>
       <c r="D13" t="n">
         <v>26.01631416254048</v>
@@ -2506,7 +2506,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
         <v>19.0517959486136</v>
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>15.0501923061036</v>
       </c>
       <c r="D15" t="n">
         <v>17.20021977840412</v>
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.87936820556466</v>
+        <v>14.05273663858884</v>
       </c>
       <c r="D16" t="n">
         <v>14.87936820556466</v>
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.11106066376691</v>
+        <v>14.16661937228147</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>10.86107485208246</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>35.50686921949439</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>3.610868056219768</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.512693285795088</v>
+        <v>2.600649668549801</v>
       </c>
       <c r="C2" t="n">
-        <v>2.547635292520473</v>
+        <v>5.058945919983814</v>
       </c>
       <c r="D2" t="n">
-        <v>7.908959505412304</v>
+        <v>7.774460069930491</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.86137795171873</v>
+        <v>18.23105486786327</v>
       </c>
       <c r="C3" t="n">
-        <v>31.38156536624929</v>
+        <v>35.91233102134833</v>
       </c>
       <c r="D3" t="n">
-        <v>56.73029108990194</v>
+        <v>60.78000036992003</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>52.85042416271855</v>
+        <v>41.40226418349649</v>
       </c>
       <c r="C4" t="n">
-        <v>131.0220851133708</v>
+        <v>111.7120895185403</v>
       </c>
       <c r="D4" t="n">
-        <v>116.651262218606</v>
+        <v>126.2871159357884</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.62796834448203</v>
+        <v>42.82874359776711</v>
       </c>
       <c r="C5" t="n">
-        <v>238.9083038284614</v>
+        <v>237.1657016534233</v>
       </c>
       <c r="D5" t="n">
-        <v>98.93562489547234</v>
+        <v>107.6486357706628</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.74725853831463</v>
+        <v>32.36233132279187</v>
       </c>
       <c r="C6" t="n">
-        <v>197.3538687508066</v>
+        <v>261.2734982789079</v>
       </c>
       <c r="D6" t="n">
-        <v>50.11331156327844</v>
+        <v>53.41394734495622</v>
       </c>
     </row>
     <row r="7">
@@ -2716,10 +2716,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.31856928226148</v>
+        <v>8.204465564390594</v>
       </c>
       <c r="C7" t="n">
-        <v>136.4216974867282</v>
+        <v>195.4100082963978</v>
       </c>
       <c r="D7" t="n">
         <v>34.97378021608837</v>
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.090361846519712</v>
+        <v>3.838633523605028</v>
       </c>
       <c r="C8" t="n">
-        <v>82.6140693123691</v>
+        <v>94.96445543179397</v>
       </c>
       <c r="D8" t="n">
-        <v>31.54355373745002</v>
+        <v>31.2097595180061</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>31.72812230584841</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>32.06093477758807</v>
+        <v>31.39530983410874</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>26.90479583488384</v>
+        <v>25.33890824661018</v>
       </c>
       <c r="D10" t="n">
-        <v>23.48831382410494</v>
+        <v>23.20360698987336</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>20.7904711328347</v>
+        <v>19.54659679155399</v>
       </c>
       <c r="D11" t="n">
-        <v>23.27821981539612</v>
+        <v>22.92282714645877</v>
       </c>
     </row>
     <row r="12">
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.05550195525234</v>
+        <v>14.97067074205961</v>
       </c>
       <c r="D12" t="n">
         <v>21.26269177857742</v>
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.78864650614645</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
         <v>15.60978849752428</v>
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>12.59876828859932</v>
       </c>
       <c r="D14" t="n">
         <v>14.44249047717483</v>
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>11.82515109765283</v>
       </c>
       <c r="D15" t="n">
         <v>12.541826921753</v>
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.81278928812512</v>
+        <v>11.98615772114931</v>
       </c>
       <c r="D16" t="n">
-        <v>9.506263020221864</v>
+        <v>9.092947236733956</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>30.22212132753381</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30.49799243242716</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>2.675262494072558</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.876340846993907</v>
+        <v>2.704714925199963</v>
       </c>
       <c r="C2" t="n">
-        <v>4.708461989567702</v>
+        <v>6.090762757147212</v>
       </c>
       <c r="D2" t="n">
-        <v>13.89762050131785</v>
+        <v>14.33940696822891</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.15742379004476</v>
+        <v>13.78864650614645</v>
       </c>
       <c r="C3" t="n">
-        <v>20.45962215650353</v>
+        <v>27.84236489243954</v>
       </c>
       <c r="D3" t="n">
-        <v>50.57964172279567</v>
+        <v>53.9863062565321</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>49.43001516112266</v>
+        <v>38.61999118966102</v>
       </c>
       <c r="C4" t="n">
-        <v>105.0371868773663</v>
+        <v>101.9996594804266</v>
       </c>
       <c r="D4" t="n">
-        <v>119.2548571302685</v>
+        <v>127.3208962683603</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>64.86897955810801</v>
+        <v>50.75635630956011</v>
       </c>
       <c r="C5" t="n">
-        <v>242.1235275598697</v>
+        <v>224.8447679651258</v>
       </c>
       <c r="D5" t="n">
-        <v>113.9809084630547</v>
+        <v>123.822929198129</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54.82275530055039</v>
+        <v>41.57996051796516</v>
       </c>
       <c r="C6" t="n">
-        <v>279.5880017016322</v>
+        <v>312.9968760771512</v>
       </c>
       <c r="D6" t="n">
-        <v>64.52340436621313</v>
+        <v>69.75611962984863</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.01453059358123</v>
+        <v>17.6066633279623</v>
       </c>
       <c r="C7" t="n">
-        <v>202.1771952217711</v>
+        <v>271.106683284644</v>
       </c>
       <c r="D7" t="n">
-        <v>39.94436884268997</v>
+        <v>39.82459562277186</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.176575718044183</v>
+        <v>5.090361846519712</v>
       </c>
       <c r="C8" t="n">
-        <v>123.1700669748048</v>
+        <v>160.2212253330794</v>
       </c>
       <c r="D8" t="n">
-        <v>33.37942194439155</v>
+        <v>33.04562772494764</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>57.79843259212245</v>
+        <v>60.23905738488002</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>32.17187226816797</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>31.60245859970483</v>
+        <v>30.03657101143117</v>
       </c>
       <c r="D10" t="n">
-        <v>24.62714116103124</v>
+        <v>24.48478774391545</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.44213062427633</v>
+        <v>17.14033316844506</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>16.1301147807751</v>
+        <v>15.08946221427348</v>
       </c>
       <c r="D13" t="n">
         <v>15.60978849752428</v>
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>13.52062938288707</v>
+      </c>
+      <c r="D14" t="n">
         <v>14.13520344574558</v>
-      </c>
-      <c r="D14" t="n">
-        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>12.90016483380309</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>11.82515109765283</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>23.1456838753228</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.94432778496098</v>
+        <v>33.52766584773283</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>4.249985811684442</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.57650688657113</v>
+        <v>1.884955592153876</v>
       </c>
       <c r="C2" t="n">
-        <v>3.401755795215198</v>
+        <v>3.661918936840602</v>
       </c>
       <c r="D2" t="n">
-        <v>9.989282890711294</v>
+        <v>10.4801567428347</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.65182372235765</v>
+        <v>12.01659189998096</v>
       </c>
       <c r="C3" t="n">
-        <v>19.86566479543421</v>
+        <v>26.51209675318512</v>
       </c>
       <c r="D3" t="n">
-        <v>50.0936766091935</v>
+        <v>53.11745953827367</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.91201222617884</v>
+        <v>34.8422260237193</v>
       </c>
       <c r="C4" t="n">
-        <v>84.97419079337843</v>
+        <v>90.46216046011808</v>
       </c>
       <c r="D4" t="n">
-        <v>119.5611624139936</v>
+        <v>126.2998786559437</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>69.94952392758525</v>
+        <v>55.02695882303374</v>
       </c>
       <c r="C5" t="n">
-        <v>229.8025938715722</v>
+        <v>218.8806506618264</v>
       </c>
       <c r="D5" t="n">
-        <v>123.7738418129166</v>
+        <v>135.211202567392</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>64.60390767796137</v>
+        <v>47.85921883432777</v>
       </c>
       <c r="C6" t="n">
-        <v>327.44722053596</v>
+        <v>342.3805848652582</v>
       </c>
       <c r="D6" t="n">
-        <v>76.1963845697077</v>
+        <v>80.50331174823846</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.67895280517807</v>
+        <v>15.69029180927252</v>
       </c>
       <c r="C7" t="n">
-        <v>268.2920126165683</v>
+        <v>333.4486442520206</v>
       </c>
       <c r="D7" t="n">
-        <v>44.13643153982385</v>
+        <v>44.37597797966008</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>4.088979188187965</v>
       </c>
       <c r="C8" t="n">
-        <v>160.9722623268283</v>
+        <v>206.7855189455057</v>
       </c>
       <c r="D8" t="n">
-        <v>34.38080460272329</v>
+        <v>34.29735604786232</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>67.11718180083317</v>
+        <v>67.00624431025328</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>31.72812230584841</v>
       </c>
     </row>
     <row r="10">
@@ -3380,10 +3380,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>32.45657910239955</v>
+        <v>30.89069151412589</v>
       </c>
       <c r="D10" t="n">
         <v>25.19655482949439</v>
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.16670148773948</v>
+        <v>22.38973814305275</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.7912318963607</v>
+        <v>16.48943444052943</v>
       </c>
       <c r="D12" t="n">
         <v>19.7439280801076</v>
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>11.18701508989241</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>10.75504610002381</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.80172802147115</v>
+        <v>3.371321616383547</v>
       </c>
       <c r="C2" t="n">
-        <v>9.879327147835653</v>
+        <v>17.58899186928585</v>
       </c>
       <c r="D2" t="n">
-        <v>8.684540191767285</v>
+        <v>11.93608858823272</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.92256510455152</v>
+        <v>9.395325529641976</v>
       </c>
       <c r="C3" t="n">
-        <v>16.66516727958961</v>
+        <v>21.05848825609408</v>
       </c>
       <c r="D3" t="n">
-        <v>46.86863540074273</v>
+        <v>50.1378552558846</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.3219407981975</v>
+        <v>29.22662915542755</v>
       </c>
       <c r="C4" t="n">
-        <v>69.12289236060943</v>
+        <v>79.89462817160542</v>
       </c>
       <c r="D4" t="n">
-        <v>117.4553135883842</v>
+        <v>122.8284187737269</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>68.86960145291376</v>
+        <v>53.84886157793756</v>
       </c>
       <c r="C5" t="n">
-        <v>198.2394051800372</v>
+        <v>197.0613079349411</v>
       </c>
       <c r="D5" t="n">
-        <v>134.2539985557513</v>
+        <v>145.5686408471958</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>75.83411966684064</v>
+        <v>57.27810630887167</v>
       </c>
       <c r="C6" t="n">
-        <v>343.6686378532301</v>
+        <v>345.681220646936</v>
       </c>
       <c r="D6" t="n">
-        <v>91.00899393138359</v>
+        <v>97.08699396837559</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>39.88448223273092</v>
+        <v>28.7455727803466</v>
       </c>
       <c r="C7" t="n">
-        <v>352.3129263891231</v>
+        <v>395.3713989496839</v>
       </c>
       <c r="D7" t="n">
-        <v>51.80191761458295</v>
+        <v>52.76010337392783</v>
       </c>
     </row>
     <row r="8">
@@ -3663,10 +3663,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.09865779651019</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>233.9062992753238</v>
+        <v>292.5706333425919</v>
       </c>
       <c r="D8" t="n">
         <v>36.88426124855267</v>
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.884374755077128</v>
+        <v>2.218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>115.1531152219253</v>
+        <v>132.7921762241278</v>
       </c>
       <c r="D9" t="n">
-        <v>33.50312215512664</v>
+        <v>32.72655972106742</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>48.40016181936776</v>
+        <v>46.83427423109409</v>
       </c>
       <c r="D10" t="n">
-        <v>26.33538216642069</v>
+        <v>26.47773558353648</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28.78680618392497</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>25.05518316008284</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>20.61179305066178</v>
+        <v>19.09302935219197</v>
       </c>
       <c r="D12" t="n">
         <v>20.17786056538469</v>
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>12.74799393964483</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.29148125717007</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>2.89321048441535</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.146542449840032</v>
+        <v>5.494841900669398</v>
       </c>
       <c r="C2" t="n">
-        <v>5.828636120113313</v>
+        <v>7.303221171892022</v>
       </c>
       <c r="D2" t="n">
-        <v>12.8039535587869</v>
+        <v>21.09088593033422</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.474405125329462</v>
+        <v>2.462223242251</v>
       </c>
       <c r="C2" t="n">
-        <v>5.69119144151876</v>
+        <v>10.41241615124167</v>
       </c>
       <c r="D2" t="n">
-        <v>6.46088164164826</v>
+        <v>8.8799079849124</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.52696183746906</v>
+        <v>12.94925221901543</v>
       </c>
       <c r="C3" t="n">
-        <v>25.46162670964103</v>
+        <v>37.18369429834794</v>
       </c>
       <c r="D3" t="n">
-        <v>50.45692325976482</v>
+        <v>55.10058990085223</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>53.19501760690918</v>
+        <v>40.80241633620168</v>
       </c>
       <c r="C4" t="n">
-        <v>103.1738297347058</v>
+        <v>113.5754466612007</v>
       </c>
       <c r="D4" t="n">
-        <v>121.6159603589821</v>
+        <v>126.6444721001343</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.98229715025711</v>
+        <v>32.7658296292373</v>
       </c>
       <c r="C5" t="n">
-        <v>293.8370878810704</v>
+        <v>294.2297869627691</v>
       </c>
       <c r="D5" t="n">
-        <v>123.8474728907351</v>
+        <v>134.3767170187822</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>24.75476836258333</v>
+        <v>17.83148355223482</v>
       </c>
       <c r="C6" t="n">
-        <v>296.050928954147</v>
+        <v>321.3692204989679</v>
       </c>
       <c r="D6" t="n">
-        <v>74.26430508774999</v>
+        <v>77.20267596656069</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.306166415004762</v>
+        <v>5.150248456478767</v>
       </c>
       <c r="C7" t="n">
-        <v>164.4486309475662</v>
+        <v>205.7105052093554</v>
       </c>
       <c r="D7" t="n">
-        <v>32.5184292077671</v>
+        <v>32.09922293805371</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.002765316663493</v>
+        <v>1.50207398749762</v>
       </c>
       <c r="C8" t="n">
-        <v>84.86718029361552</v>
+        <v>97.88515485192822</v>
       </c>
       <c r="D8" t="n">
-        <v>24.61732368398877</v>
+        <v>24.11663235482289</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>36.94218436310322</v>
+        <v>35.72187196672443</v>
       </c>
       <c r="D9" t="n">
-        <v>20.07968579496001</v>
+        <v>20.1906232855399</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>22.49183990429443</v>
+        <v>20.92595231602077</v>
       </c>
       <c r="D10" t="n">
-        <v>19.64477156197868</v>
+        <v>18.93300447639974</v>
       </c>
     </row>
     <row r="11">
@@ -4330,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.52575910558656</v>
+        <v>15.28188476430585</v>
       </c>
       <c r="D11" t="n">
         <v>16.17036643664921</v>
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.84831213192725</v>
+        <v>10.41437964665016</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>13.0179745583127</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>10.14636252339079</v>
+        <v>9.365873098514571</v>
       </c>
       <c r="D13" t="n">
-        <v>9.626036240139976</v>
+        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>2.150027472300515</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.582037519898116</v>
+        <v>6.343071917138642</v>
       </c>
       <c r="C2" t="n">
-        <v>5.60479764354504</v>
+        <v>6.806456833543137</v>
       </c>
       <c r="D2" t="n">
-        <v>12.02935462013617</v>
+        <v>22.95424307299467</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.29348581030757</v>
+        <v>11.67298020349457</v>
       </c>
       <c r="C3" t="n">
-        <v>14.68694565553228</v>
+        <v>18.40286071610646</v>
       </c>
       <c r="D3" t="n">
-        <v>13.89173001509237</v>
+        <v>20.85232123820225</v>
       </c>
     </row>
     <row r="4">
@@ -4557,7 +4557,7 @@
         <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>9.449321653375552</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4571,7 +4571,7 @@
         <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>18.43525839034661</v>
       </c>
       <c r="D6" t="n">
         <v>32.8453511932813</v>
@@ -4585,7 +4585,7 @@
         <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>20.72076704583318</v>
       </c>
       <c r="D7" t="n">
         <v>32.21899615797182</v>
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>8.845546815263761</v>
       </c>
       <c r="C8" t="n">
         <v>21.69662426385451</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>8.764061755811273</v>
       </c>
       <c r="C9" t="n">
         <v>22.74218556887735</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>39.60468413702056</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>25.62361508084176</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>50.1084028247572</v>
       </c>
     </row>
     <row r="11">
@@ -4697,7 +4697,7 @@
         <v>5.375068680751286</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
         <v>42.28387362191012</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39740514717965</v>
+        <v>13.39618835276138</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13935635876406</v>
+        <v>70.1329860821037</v>
       </c>
       <c r="D21" t="n">
-        <v>1.5761653114329</v>
+        <v>1.576022159148398</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.334817024877167</v>
+        <v>6.082908775513236</v>
       </c>
       <c r="C2" t="n">
-        <v>4.329507375728434</v>
+        <v>7.422994391810134</v>
       </c>
       <c r="D2" t="n">
-        <v>12.06666103289755</v>
+        <v>20.53718022513903</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.68328070662255</v>
+        <v>17.80890335503714</v>
       </c>
       <c r="C3" t="n">
-        <v>19.17353266394021</v>
+        <v>23.49322256262617</v>
       </c>
       <c r="D3" t="n">
-        <v>20.63633674326795</v>
+        <v>35.09257168830224</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>19.97365704290135</v>
+        <v>13.61782240560751</v>
       </c>
       <c r="C4" t="n">
-        <v>22.94737083906494</v>
+        <v>28.60125586782233</v>
       </c>
       <c r="D4" t="n">
-        <v>22.34752299177014</v>
+        <v>25.99766095615978</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.375068680751288</v>
+        <v>5.522330836388309</v>
       </c>
       <c r="D5" t="n">
         <v>29.40334374219198</v>
@@ -4882,7 +4882,7 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>16.42267559664065</v>
       </c>
       <c r="D6" t="n">
         <v>34.57617239586842</v>
@@ -4893,10 +4893,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.37385025333556</v>
       </c>
       <c r="D7" t="n">
         <v>34.97378021608837</v>
@@ -4907,10 +4907,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>9.513135254151592</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>25.45180923259856</v>
       </c>
       <c r="D8" t="n">
         <v>36.63391558396972</v>
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>9.429686699290611</v>
       </c>
       <c r="C9" t="n">
         <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>40.60312155223957</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>8.825911861178826</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>49.68134257340984</v>
       </c>
     </row>
     <row r="11">
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>28.8565102709265</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5025,7 +5025,7 @@
         <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>36.36098972218912</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44003704986589</v>
+        <v>15.43577311844927</v>
       </c>
       <c r="C21" t="n">
-        <v>86.13915406767288</v>
+        <v>86.11536581871698</v>
       </c>
       <c r="D21" t="n">
-        <v>3.25053411576124</v>
+        <v>3.24963644598932</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.162430339557228</v>
+        <v>4.978442608235575</v>
       </c>
       <c r="C2" t="n">
-        <v>4.216606389740051</v>
+        <v>10.94943214546467</v>
       </c>
       <c r="D2" t="n">
-        <v>23.65815617693964</v>
+        <v>21.48260326432871</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.31236000086651</v>
+        <v>19.65949777754238</v>
       </c>
       <c r="C3" t="n">
-        <v>17.7598159698248</v>
+        <v>26.69372007847078</v>
       </c>
       <c r="D3" t="n">
-        <v>25.5008966178109</v>
+        <v>43.37852231214532</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.46385224695678</v>
+        <v>25.47438942979624</v>
       </c>
       <c r="C4" t="n">
-        <v>37.70107533848601</v>
+        <v>45.80540263704343</v>
       </c>
       <c r="D4" t="n">
-        <v>27.6695772964921</v>
+        <v>37.72660077879643</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>17.22967220953153</v>
+        <v>12.00186568441726</v>
       </c>
       <c r="C5" t="n">
-        <v>26.45810062945155</v>
+        <v>32.47130531796326</v>
       </c>
       <c r="D5" t="n">
-        <v>30.67961575771283</v>
+        <v>31.98043146583985</v>
       </c>
     </row>
     <row r="6">
@@ -5190,10 +5190,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.07549676223577</v>
+        <v>12.31700669748049</v>
       </c>
       <c r="D6" t="n">
         <v>36.54850353370026</v>
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.37385025333556</v>
       </c>
       <c r="D7" t="n">
-        <v>37.12969817461437</v>
+        <v>37.4890178343687</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>29.37389131106456</v>
       </c>
       <c r="D8" t="n">
-        <v>38.38633523605029</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>9.984374152190059</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>29.62030998483051</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>41.49062147687869</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>29.46715734296802</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>48.9695754878309</v>
       </c>
     </row>
     <row r="11">
@@ -5263,10 +5263,10 @@
         <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>49.57727731675966</v>
       </c>
     </row>
     <row r="12">
@@ -5277,10 +5277,10 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>46.2138096820101</v>
       </c>
     </row>
     <row r="13">
@@ -5291,10 +5291,10 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
-        <v>45.52854978444583</v>
+        <v>45.00822350119503</v>
       </c>
     </row>
     <row r="14">
@@ -5305,7 +5305,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
         <v>45.47848065152925</v>
@@ -5316,7 +5316,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
         <v>27.5920192278566</v>
@@ -5333,10 +5333,10 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5350,7 +5350,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73465211492304</v>
+        <v>16.72461288220887</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0813779010306</v>
+        <v>102.0201385814741</v>
       </c>
       <c r="D21" t="n">
-        <v>5.020395634476913</v>
+        <v>4.181153220552217</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.003387211469246</v>
+        <v>5.983752257384309</v>
       </c>
       <c r="C2" t="n">
-        <v>3.204424506661589</v>
+        <v>11.96161402854314</v>
       </c>
       <c r="D2" t="n">
-        <v>21.38442849390403</v>
+        <v>18.27523351455438</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.75414646777757</v>
+        <v>18.20160243673586</v>
       </c>
       <c r="C3" t="n">
-        <v>16.94496537529995</v>
+        <v>35.61780671007428</v>
       </c>
       <c r="D3" t="n">
-        <v>37.80710409054467</v>
+        <v>50.05440670102362</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.82044764777662</v>
+        <v>31.95785126864217</v>
       </c>
       <c r="C4" t="n">
-        <v>41.46607778427253</v>
+        <v>56.87068101160924</v>
       </c>
       <c r="D4" t="n">
-        <v>33.87225929192346</v>
+        <v>50.25959197121121</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.57577148524092</v>
+        <v>25.08365384350601</v>
       </c>
       <c r="C5" t="n">
-        <v>49.50462798664542</v>
+        <v>60.62292073724056</v>
       </c>
       <c r="D5" t="n">
-        <v>33.33033455917922</v>
+        <v>37.69911184307752</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.6516027381794</v>
+        <v>10.98870205363455</v>
       </c>
       <c r="C6" t="n">
-        <v>27.85414586489051</v>
+        <v>32.60384125803657</v>
       </c>
       <c r="D6" t="n">
-        <v>38.40007970390975</v>
+        <v>38.76234460677682</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.623671834103982</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>21.13997331554657</v>
       </c>
       <c r="D7" t="n">
-        <v>39.22572952318131</v>
+        <v>39.52516257297658</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.93176068678823</v>
+        <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
         <v>31.54355373745002</v>
       </c>
       <c r="D8" t="n">
-        <v>40.13875488813084</v>
+        <v>39.8884092235479</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>34.39062207976576</v>
+        <v>33.9468721174462</v>
       </c>
       <c r="D9" t="n">
-        <v>41.82343394861835</v>
+        <v>42.3781214015178</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>9.82238578098934</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>33.02599277086271</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>48.54251523648354</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9.062513057902304</v>
+        <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>50.6434553235717</v>
       </c>
     </row>
     <row r="12">
@@ -5588,10 +5588,10 @@
         <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>34.28066633689012</v>
       </c>
       <c r="D12" t="n">
-        <v>46.86470840992573</v>
+        <v>47.08167465256428</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>32.5203927031756</v>
       </c>
       <c r="D13" t="n">
-        <v>46.30903920932205</v>
+        <v>45.78871292607123</v>
       </c>
     </row>
     <row r="14">
@@ -5616,10 +5616,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5633,7 +5633,7 @@
         <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>41.74489413227862</v>
       </c>
     </row>
     <row r="17">
@@ -5661,7 +5661,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5686,7 +5686,7 @@
         <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.06161037915328</v>
+        <v>18.04309872256792</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8305058068571</v>
+        <v>117.709739285324</v>
       </c>
       <c r="D21" t="n">
-        <v>6.880613477772677</v>
+        <v>6.014366240855973</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.927612711792993</v>
+        <v>6.35583463729385</v>
       </c>
       <c r="C2" t="n">
-        <v>9.857728698342223</v>
+        <v>12.67828985264331</v>
       </c>
       <c r="D2" t="n">
-        <v>24.76753108273853</v>
+        <v>19.17844140246144</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.60902773399829</v>
+        <v>17.24439842509522</v>
       </c>
       <c r="C3" t="n">
-        <v>13.49412219487241</v>
+        <v>39.13246349127786</v>
       </c>
       <c r="D3" t="n">
-        <v>42.94655332227672</v>
+        <v>49.68625131193107</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.98864530037232</v>
+        <v>24.28745645536184</v>
       </c>
       <c r="C4" t="n">
-        <v>34.81670058340888</v>
+        <v>61.92471819307181</v>
       </c>
       <c r="D4" t="n">
-        <v>38.61999118966102</v>
+        <v>55.19876467127691</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.29258617806133</v>
+        <v>22.21204180858409</v>
       </c>
       <c r="C5" t="n">
-        <v>47.83565688942584</v>
+        <v>62.73367830137119</v>
       </c>
       <c r="D5" t="n">
-        <v>30.90050899116836</v>
+        <v>37.5518496874405</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>16.62393387601124</v>
+        <v>12.27675504160637</v>
       </c>
       <c r="C6" t="n">
-        <v>36.66925850132262</v>
+        <v>44.1560664939088</v>
       </c>
       <c r="D6" t="n">
-        <v>31.31578827006476</v>
+        <v>32.48308629041422</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.467753875577986</v>
+        <v>5.389794896314989</v>
       </c>
       <c r="C7" t="n">
-        <v>20.00212772632452</v>
+        <v>21.73883941513712</v>
       </c>
       <c r="D7" t="n">
-        <v>30.60205768907732</v>
+        <v>30.84160412891355</v>
       </c>
     </row>
     <row r="8">
@@ -5846,7 +5846,7 @@
         <v>18.60902773399829</v>
       </c>
       <c r="D8" t="n">
-        <v>30.12492830481337</v>
+        <v>30.0414797499524</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.96562313481813</v>
+        <v>21.74374815365835</v>
       </c>
       <c r="D9" t="n">
-        <v>29.84218496599028</v>
+        <v>30.39687241888974</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.6377194015997</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.02599277086271</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.07968579496001</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>34.65078522139116</v>
       </c>
     </row>
     <row r="12">
@@ -5902,7 +5902,7 @@
         <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.67707142522758</v>
       </c>
     </row>
     <row r="13">
@@ -5913,7 +5913,7 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>18.73174619702914</v>
       </c>
       <c r="D13" t="n">
         <v>30.43908757017236</v>
@@ -5930,7 +5930,7 @@
         <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>29.49955501720816</v>
       </c>
     </row>
     <row r="15">
@@ -5944,7 +5944,7 @@
         <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>27.95035713990669</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -5997,7 +5997,7 @@
         <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
         <v>15.64709491028566</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.060661564772726</v>
+        <v>7.048591643635808</v>
       </c>
       <c r="C21" t="n">
-        <v>66.1937021697443</v>
+        <v>66.0805466590857</v>
       </c>
       <c r="D21" t="n">
-        <v>5.295496173579544</v>
+        <v>4.40536977727238</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.33129094468768</v>
+        <v>5.307328089158257</v>
       </c>
       <c r="C2" t="n">
-        <v>9.65254342815464</v>
+        <v>8.72577359534565</v>
       </c>
       <c r="D2" t="n">
-        <v>22.38090241371453</v>
+        <v>21.44136986075034</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.25407703341745</v>
+        <v>20.2681813541754</v>
       </c>
       <c r="C3" t="n">
-        <v>29.89912633283661</v>
+        <v>45.71508184825273</v>
       </c>
       <c r="D3" t="n">
-        <v>53.95194508688346</v>
+        <v>53.78995671568274</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.28517416478385</v>
+        <v>30.2093586073786</v>
       </c>
       <c r="C4" t="n">
-        <v>34.2551408965797</v>
+        <v>84.336054785618</v>
       </c>
       <c r="D4" t="n">
-        <v>52.86318688287376</v>
+        <v>68.43370547222817</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.44738352016284</v>
+        <v>30.36054775383262</v>
       </c>
       <c r="C5" t="n">
-        <v>58.21763886183587</v>
+        <v>93.87962421860125</v>
       </c>
       <c r="D5" t="n">
-        <v>38.68085954732433</v>
+        <v>49.21010367537139</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.6591789823729</v>
+        <v>22.50067563363265</v>
       </c>
       <c r="C6" t="n">
-        <v>60.25672884355649</v>
+        <v>75.87437132271475</v>
       </c>
       <c r="D6" t="n">
-        <v>34.25415914887547</v>
+        <v>37.59504658642736</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.13323995033708</v>
+        <v>10.65981657271187</v>
       </c>
       <c r="C7" t="n">
-        <v>39.58504918293564</v>
+        <v>46.23246288839079</v>
       </c>
       <c r="D7" t="n">
-        <v>33.41672835715293</v>
+        <v>33.77604801690726</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.342090169434394</v>
+        <v>5.591053175685585</v>
       </c>
       <c r="C8" t="n">
-        <v>23.44904391593506</v>
+        <v>24.86766934857171</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>31.71045084717197</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>23.18593553119691</v>
       </c>
       <c r="D9" t="n">
-        <v>30.95155987178918</v>
+        <v>31.72812230584841</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.91184799526281</v>
+        <v>24.48478774391545</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>33.31069960509428</v>
       </c>
     </row>
     <row r="11">
@@ -6196,7 +6196,7 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
         <v>35.36157055926586</v>
@@ -6210,7 +6210,7 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
         <v>32.97886888105885</v>
@@ -6224,10 +6224,10 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>30.69925071179776</v>
       </c>
     </row>
     <row r="14">
@@ -6238,7 +6238,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6252,7 +6252,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.286108057246259</v>
+        <v>7.266105485797802</v>
       </c>
       <c r="C21" t="n">
-        <v>76.50413460108572</v>
+        <v>75.38584441515221</v>
       </c>
       <c r="D21" t="n">
-        <v>6.375344550090476</v>
+        <v>5.449579114348351</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.362305960596078</v>
+        <v>5.404521111878692</v>
       </c>
       <c r="C2" t="n">
-        <v>7.514296928305087</v>
+        <v>6.014186436215961</v>
       </c>
       <c r="D2" t="n">
-        <v>18.01016163440774</v>
+        <v>23.13193940746335</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.9925312334603</v>
+        <v>19.16862392541897</v>
       </c>
       <c r="C3" t="n">
-        <v>34.64587648286994</v>
+        <v>38.76430810218531</v>
       </c>
       <c r="D3" t="n">
-        <v>59.33683124467722</v>
+        <v>58.11946409141117</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.60646770597982</v>
+        <v>35.4420738710141</v>
       </c>
       <c r="C4" t="n">
-        <v>58.58088551240717</v>
+        <v>100.6595738641297</v>
       </c>
       <c r="D4" t="n">
-        <v>67.52755234120836</v>
+        <v>78.72045791732624</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.00684084286328</v>
+        <v>38.18998569520093</v>
       </c>
       <c r="C5" t="n">
-        <v>61.26105674500098</v>
+        <v>128.6334929489384</v>
       </c>
       <c r="D5" t="n">
-        <v>49.57825906446394</v>
+        <v>62.73367830137119</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.49316580936395</v>
+        <v>32.52333794628834</v>
       </c>
       <c r="C6" t="n">
-        <v>78.49072895453251</v>
+        <v>115.4820007028481</v>
       </c>
       <c r="D6" t="n">
-        <v>39.08435785376978</v>
+        <v>44.1560664939088</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.03260296288517</v>
+        <v>18.98405535702057</v>
       </c>
       <c r="C7" t="n">
-        <v>65.63572451512475</v>
+        <v>80.12828412521617</v>
       </c>
       <c r="D7" t="n">
-        <v>35.81219275551515</v>
+        <v>37.30935800449154</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.34900346109313</v>
+        <v>8.845546815263761</v>
       </c>
       <c r="C8" t="n">
-        <v>39.8884092235479</v>
+        <v>43.97738841173587</v>
       </c>
       <c r="D8" t="n">
-        <v>34.29735604786232</v>
+        <v>33.88011327355743</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.101561981893925</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>27.17968519207294</v>
+        <v>27.84531013555227</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>32.72655972106742</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>26.76244241776806</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>34.02246669067321</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.264712027248144</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.53926689373453</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>34.06370009425158</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>31.47974013667398</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.81737923147687</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -6605,7 +6605,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -6619,10 +6619,10 @@
         <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>19.50241814486288</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.499622103597684</v>
+        <v>7.468718114038479</v>
       </c>
       <c r="C21" t="n">
-        <v>86.24565419137336</v>
+        <v>84.02307878293288</v>
       </c>
       <c r="D21" t="n">
-        <v>7.499622103597684</v>
+        <v>6.535128349783669</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_53_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_53_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497629824495</v>
+        <v>10.84497639000846</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907182354144</v>
+        <v>37.78907214328928</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.908157684157304</v>
+        <v>6.101561981893926</v>
       </c>
       <c r="C2" t="n">
-        <v>5.701990666265475</v>
+        <v>7.35918079103409</v>
       </c>
       <c r="D2" t="n">
-        <v>23.04554560948963</v>
+        <v>23.18397203578843</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.6532063806894</v>
+        <v>15.07964473723101</v>
       </c>
       <c r="C3" t="n">
-        <v>30.37036523087508</v>
+        <v>31.10667600906019</v>
       </c>
       <c r="D3" t="n">
-        <v>62.4047928204485</v>
+        <v>77.58752106662543</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.1950743601714</v>
+        <v>30.38803668955152</v>
       </c>
       <c r="C4" t="n">
-        <v>97.66033462765571</v>
+        <v>68.15292562881358</v>
       </c>
       <c r="D4" t="n">
-        <v>88.82853228025141</v>
+        <v>96.46063893306611</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.18493808795945</v>
+        <v>38.97538385859838</v>
       </c>
       <c r="C5" t="n">
-        <v>157.7423123798563</v>
+        <v>105.6360529769568</v>
       </c>
       <c r="D5" t="n">
-        <v>74.68645660057611</v>
+        <v>68.69779560467057</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.02272873258048</v>
+        <v>38.68184129502858</v>
       </c>
       <c r="C6" t="n">
-        <v>158.0682526176662</v>
+        <v>129.5700802587898</v>
       </c>
       <c r="D6" t="n">
-        <v>53.13218575383738</v>
+        <v>46.12839763174064</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.26647990067416</v>
+        <v>28.14670668075605</v>
       </c>
       <c r="C7" t="n">
-        <v>123.186756685777</v>
+        <v>114.8625179014683</v>
       </c>
       <c r="D7" t="n">
-        <v>40.96244121199391</v>
+        <v>38.86640986342697</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.43659999094934</v>
+        <v>14.85384276525424</v>
       </c>
       <c r="C8" t="n">
-        <v>74.43611093599316</v>
+        <v>73.1009340582175</v>
       </c>
       <c r="D8" t="n">
-        <v>36.30012136452581</v>
+        <v>35.9663271450819</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.321874378272709</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>40.71405904281946</v>
+        <v>39.71562162760046</v>
       </c>
       <c r="D9" t="n">
-        <v>33.83593462686631</v>
+        <v>34.39062207976576</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>5.551783267515713</v>
       </c>
       <c r="C10" t="n">
         <v>30.46363126277853</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>28.60910984945629</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.33774657245668</v>
+        <v>27.55471281509523</v>
       </c>
       <c r="D12" t="n">
-        <v>34.49763257952867</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>24.97566159603886</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>23.35381438862312</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>18.59921025695582</v>
+        <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1010,7 +1010,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1021,7 +1021,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.655201123592103</v>
+        <v>7.684994079856874</v>
       </c>
       <c r="C21" t="n">
-        <v>92.81931362355425</v>
+        <v>93.18055321826459</v>
       </c>
       <c r="D21" t="n">
-        <v>7.655201123592103</v>
+        <v>8.645618339838983</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.180101798233672</v>
+        <v>6.285148802588081</v>
       </c>
       <c r="C2" t="n">
-        <v>7.712609964562943</v>
+        <v>7.015569094547707</v>
       </c>
       <c r="D2" t="n">
-        <v>19.00172681569702</v>
+        <v>29.21975692149782</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.98700060013331</v>
+        <v>17.82853830912208</v>
       </c>
       <c r="C3" t="n">
-        <v>26.10467145592269</v>
+        <v>29.64878066825367</v>
       </c>
       <c r="D3" t="n">
-        <v>65.07023783747859</v>
+        <v>77.58261232810419</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.64627739349744</v>
+        <v>29.22662915542755</v>
       </c>
       <c r="C4" t="n">
-        <v>87.00346329805657</v>
+        <v>72.8368439257751</v>
       </c>
       <c r="D4" t="n">
-        <v>96.54997797415255</v>
+        <v>110.7038346262788</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.81740459367266</v>
+        <v>41.87153958612647</v>
       </c>
       <c r="C5" t="n">
-        <v>166.209886328985</v>
+        <v>114.1281706186917</v>
       </c>
       <c r="D5" t="n">
-        <v>87.17919613711678</v>
+        <v>83.89034132788996</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.15356321915257</v>
+        <v>45.16235789076178</v>
       </c>
       <c r="C6" t="n">
-        <v>200.0507296943726</v>
+        <v>148.0053386491364</v>
       </c>
       <c r="D6" t="n">
-        <v>61.86679507852126</v>
+        <v>55.70829172978102</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>37.72856427420492</v>
+        <v>36.83026512481909</v>
       </c>
       <c r="C7" t="n">
-        <v>169.1197865243725</v>
+        <v>148.039699818785</v>
       </c>
       <c r="D7" t="n">
-        <v>46.11268966847268</v>
+        <v>42.4596064609703</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21.61317570899353</v>
+        <v>21.94696992843745</v>
       </c>
       <c r="C8" t="n">
-        <v>114.407968714402</v>
+        <v>110.485886635936</v>
       </c>
       <c r="D8" t="n">
-        <v>38.38633523605029</v>
+        <v>38.21943812632832</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.42812411450962</v>
+        <v>10.87187407682917</v>
       </c>
       <c r="C9" t="n">
-        <v>63.12343213995715</v>
+        <v>62.90155715879737</v>
       </c>
       <c r="D9" t="n">
-        <v>35.38905949498476</v>
+        <v>35.49999698556465</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.121196935978863</v>
+        <v>6.405903770210439</v>
       </c>
       <c r="C10" t="n">
-        <v>38.43542262126263</v>
+        <v>38.57777603837842</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>35.87306111317846</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>31.98534020436108</v>
+        <v>32.34073287329842</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.42774856607789</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>29.72437524148068</v>
+        <v>30.59224021203486</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>27.57729301229291</v>
+        <v>27.83745615391831</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>24.89024954576939</v>
+        <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>31.34327720578367</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.83915760741954</v>
+        <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1321,7 +1321,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1332,7 +1332,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.825187457957212</v>
+        <v>7.864929290832857</v>
       </c>
       <c r="C21" t="n">
-        <v>100.7492885211991</v>
+        <v>101.260964619473</v>
       </c>
       <c r="D21" t="n">
-        <v>8.803335890201865</v>
+        <v>9.83116161354107</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.731844008020379</v>
+        <v>6.476589604916207</v>
       </c>
       <c r="C2" t="n">
-        <v>13.33802430989717</v>
+        <v>10.10709261522091</v>
       </c>
       <c r="D2" t="n">
-        <v>19.14800722362979</v>
+        <v>30.17303394232147</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.25207248027995</v>
+        <v>18.96736564604837</v>
       </c>
       <c r="C3" t="n">
-        <v>27.5478405811655</v>
+        <v>28.27924262082937</v>
       </c>
       <c r="D3" t="n">
-        <v>64.49591543049421</v>
+        <v>80.83710596768236</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.88051418418493</v>
+        <v>30.69434197327653</v>
       </c>
       <c r="C4" t="n">
-        <v>76.44869372969913</v>
+        <v>72.45396232111885</v>
       </c>
       <c r="D4" t="n">
-        <v>104.0672201455704</v>
+        <v>119.3697216116654</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.19185137961819</v>
+        <v>42.85328729037328</v>
       </c>
       <c r="C5" t="n">
-        <v>161.595672119025</v>
+        <v>121.6139968635737</v>
       </c>
       <c r="D5" t="n">
-        <v>96.92304210176638</v>
+        <v>99.10743074371554</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>56.19131160027045</v>
+        <v>49.71079500453725</v>
       </c>
       <c r="C6" t="n">
-        <v>226.858332506536</v>
+        <v>162.8179480108123</v>
       </c>
       <c r="D6" t="n">
-        <v>71.92970904705108</v>
+        <v>66.73724543928969</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>46.77144237802229</v>
+        <v>43.89688509998763</v>
       </c>
       <c r="C7" t="n">
-        <v>216.4900950019854</v>
+        <v>175.4677671800324</v>
       </c>
       <c r="D7" t="n">
-        <v>51.02339168511523</v>
+        <v>47.13076203777662</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>28.95664853675967</v>
+        <v>29.37389131106456</v>
       </c>
       <c r="C8" t="n">
-        <v>158.3853571261379</v>
+        <v>146.8694565553228</v>
       </c>
       <c r="D8" t="n">
-        <v>41.22358610132356</v>
+        <v>40.63944621729671</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.75468624712531</v>
+        <v>15.53124868118453</v>
       </c>
       <c r="C9" t="n">
-        <v>95.29530440812512</v>
+        <v>94.96249193638545</v>
       </c>
       <c r="D9" t="n">
-        <v>36.49843440078366</v>
+        <v>36.72030938194344</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>8.114144775599888</v>
       </c>
       <c r="C10" t="n">
-        <v>52.52841091572559</v>
+        <v>53.38253141842032</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>36.72718161587318</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>36.96083756948391</v>
+        <v>37.49392657288993</v>
       </c>
       <c r="D11" t="n">
-        <v>36.96083756948391</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>32.54493639578176</v>
+        <v>33.62976760897449</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>36.23336252063703</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>29.65859814529614</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>26.73397173434489</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>31.65056423721292</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.00864010735575</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1604,7 +1604,7 @@
         <v>21.49242074137117</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1615,7 +1615,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1632,7 +1632,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.979196664672824</v>
+        <v>8.028992063779381</v>
       </c>
       <c r="C21" t="n">
-        <v>107.7191549730831</v>
+        <v>109.3950168689941</v>
       </c>
       <c r="D21" t="n">
-        <v>9.97399583084103</v>
+        <v>11.03986408769665</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.278276568658352</v>
+        <v>6.028912651779663</v>
       </c>
       <c r="C2" t="n">
-        <v>9.282424543653592</v>
+        <v>6.872233929727672</v>
       </c>
       <c r="D2" t="n">
-        <v>15.93671048303847</v>
+        <v>24.91381149067131</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.39995653072273</v>
+        <v>22.01569226773472</v>
       </c>
       <c r="C3" t="n">
-        <v>46.08323723734528</v>
+        <v>44.71369918992098</v>
       </c>
       <c r="D3" t="n">
-        <v>71.1128949571177</v>
+        <v>87.82714962191966</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.10877837318892</v>
+        <v>20.58626761035137</v>
       </c>
       <c r="C4" t="n">
-        <v>121.0288752318425</v>
+        <v>100.3532685804047</v>
       </c>
       <c r="D4" t="n">
-        <v>102.7654226897391</v>
+        <v>113.5371585007351</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.63681976935347</v>
+        <v>28.00435326364027</v>
       </c>
       <c r="C5" t="n">
-        <v>135.5548142638784</v>
+        <v>97.29119749085893</v>
       </c>
       <c r="D5" t="n">
-        <v>69.01686360855078</v>
+        <v>66.51340696272142</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.02144388523996</v>
+        <v>27.25037102677872</v>
       </c>
       <c r="C6" t="n">
-        <v>142.5713651061303</v>
+        <v>115.5625040145963</v>
       </c>
       <c r="D6" t="n">
-        <v>33.56988099901544</v>
+        <v>31.03402667894593</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.16371518689774</v>
+        <v>19.46314823669301</v>
       </c>
       <c r="C7" t="n">
-        <v>111.3890945238431</v>
+        <v>103.2445155694116</v>
       </c>
       <c r="D7" t="n">
-        <v>28.98511922018283</v>
+        <v>28.56591295046944</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.18072369303942</v>
+        <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>70.18023463808323</v>
+        <v>69.9298889735003</v>
       </c>
       <c r="D8" t="n">
-        <v>26.8704346652352</v>
+        <v>27.03733177495716</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.324999547834698</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>40.04843409934012</v>
+        <v>40.71405904281946</v>
       </c>
       <c r="D9" t="n">
-        <v>27.06874770149305</v>
+        <v>27.95624762613216</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.701188845010476</v>
+        <v>3.843542262126263</v>
       </c>
       <c r="C10" t="n">
-        <v>28.89774367450487</v>
+        <v>29.32480392585223</v>
       </c>
       <c r="D10" t="n">
-        <v>28.89774367450487</v>
+        <v>28.61303684027329</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>27.8983245115816</v>
+        <v>28.96450251839364</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>24.0832529328785</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>27.12078032981814</v>
+        <v>26.68684784454105</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>22.11386703815941</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>24.97566159603886</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>19.97365704290136</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>24.58296251434014</v>
+        <v>23.66110142005238</v>
       </c>
     </row>
     <row r="15">
@@ -1901,7 +1901,7 @@
         <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>22.21695054710532</v>
+        <v>22.57528845915541</v>
       </c>
     </row>
     <row r="16">
@@ -1912,7 +1912,7 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.11931555602838</v>
+        <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
         <v>20.66578917439536</v>
@@ -1929,7 +1929,7 @@
         <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1940,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>15.51652246562084</v>
+        <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
         <v>13.9113649691773</v>
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>72.62969516017901</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>7.397468951499714</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.852377991464484</v>
+        <v>3.677626900108552</v>
       </c>
       <c r="C2" t="n">
-        <v>4.76442160870977</v>
+        <v>3.468514639103981</v>
       </c>
       <c r="D2" t="n">
-        <v>11.87522023056942</v>
+        <v>18.63749841742145</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.14961086613979</v>
+        <v>22.02550974477719</v>
       </c>
       <c r="C3" t="n">
-        <v>42.00898426472102</v>
+        <v>36.33939127269569</v>
       </c>
       <c r="D3" t="n">
-        <v>68.86469271439252</v>
+        <v>87.76333602114362</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.71085175779947</v>
+        <v>29.72437524148068</v>
       </c>
       <c r="C4" t="n">
-        <v>122.6114525310884</v>
+        <v>108.4831213192725</v>
       </c>
       <c r="D4" t="n">
-        <v>112.4523272875424</v>
+        <v>129.8989657397125</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.19565519724816</v>
+        <v>30.92505268377453</v>
       </c>
       <c r="C5" t="n">
-        <v>176.1746255270901</v>
+        <v>139.4327176956533</v>
       </c>
       <c r="D5" t="n">
-        <v>84.94572010995527</v>
+        <v>84.70028318389357</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.97239755775664</v>
+        <v>32.00006641992479</v>
       </c>
       <c r="C6" t="n">
-        <v>178.0733255871035</v>
+        <v>137.7814180571101</v>
       </c>
       <c r="D6" t="n">
-        <v>41.0164373357275</v>
+        <v>39.04410619789565</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.90609637775757</v>
+        <v>18.38518925743002</v>
       </c>
       <c r="C7" t="n">
-        <v>145.7041220303819</v>
+        <v>129.4149641215188</v>
       </c>
       <c r="D7" t="n">
-        <v>31.56024344842221</v>
+        <v>31.14103717870882</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.428304040958867</v>
+        <v>9.012443924985718</v>
       </c>
       <c r="C8" t="n">
-        <v>94.38031554776711</v>
+        <v>92.79479300540851</v>
       </c>
       <c r="D8" t="n">
-        <v>27.62147165898401</v>
+        <v>28.28906009787184</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.326562132615692</v>
+        <v>4.659374604355361</v>
       </c>
       <c r="C9" t="n">
-        <v>43.93124626963626</v>
+        <v>45.70624611891449</v>
       </c>
       <c r="D9" t="n">
-        <v>28.39999758845172</v>
+        <v>28.84374755077128</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>31.46010518258904</v>
+        <v>32.17187226816798</v>
       </c>
       <c r="D10" t="n">
-        <v>29.60951076008381</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>28.78680618392497</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
-        <v>29.14219885286231</v>
+        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>21.04572553593887</v>
       </c>
       <c r="D12" t="n">
-        <v>27.98864530037232</v>
+        <v>28.42257778564941</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.3902779224005</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>25.23582473766426</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>18.4372218857551</v>
+        <v>18.74450891718435</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
         <v>17.5585576904542</v>
@@ -2226,7 +2226,7 @@
         <v>13.22610507161303</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.22217808079604</v>
+        <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
         <v>11.8055161435679</v>
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>63.19019098384595</v>
+        <v>63.79200232654924</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>6.018113427032947</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.285328729037327</v>
+        <v>4.462043315801753</v>
       </c>
       <c r="C2" t="n">
-        <v>10.5115726693706</v>
+        <v>5.055018929166827</v>
       </c>
       <c r="D2" t="n">
-        <v>11.13989120008856</v>
+        <v>17.54088623177776</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.14760631300229</v>
+        <v>17.39656931925348</v>
       </c>
       <c r="C3" t="n">
-        <v>29.69295931494478</v>
+        <v>24.30807315715103</v>
       </c>
       <c r="D3" t="n">
-        <v>62.94475405778425</v>
+        <v>83.34547135203297</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.79041437957247</v>
+        <v>35.4420738710141</v>
       </c>
       <c r="C4" t="n">
-        <v>113.6264975418216</v>
+        <v>99.37053912845366</v>
       </c>
       <c r="D4" t="n">
-        <v>119.892993138029</v>
+        <v>141.985261726695</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.50338419703392</v>
+        <v>37.25732537616646</v>
       </c>
       <c r="C5" t="n">
-        <v>201.6509784522949</v>
+        <v>169.0569546713008</v>
       </c>
       <c r="D5" t="n">
-        <v>102.5190040159732</v>
+        <v>107.4768299224196</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.29190752999335</v>
+        <v>36.95102009244145</v>
       </c>
       <c r="C6" t="n">
-        <v>224.2822265305924</v>
+        <v>178.7576037369635</v>
       </c>
       <c r="D6" t="n">
-        <v>54.6214970211798</v>
+        <v>52.89067581859268</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.35010838198439</v>
+        <v>26.11056194214817</v>
       </c>
       <c r="C7" t="n">
-        <v>197.2664932051286</v>
+        <v>163.191012138426</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>34.49468733641593</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.43383467428585</v>
+        <v>13.18487166803466</v>
       </c>
       <c r="C8" t="n">
-        <v>137.8570126303371</v>
+        <v>128.7611201504904</v>
       </c>
       <c r="D8" t="n">
-        <v>29.37389131106456</v>
+        <v>29.87458264023044</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>73.88436872620643</v>
+        <v>74.99374363200533</v>
       </c>
       <c r="D9" t="n">
-        <v>29.28749751309084</v>
+        <v>29.50937249425062</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.562361508084175</v>
+        <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>40.28601704376787</v>
+        <v>41.85190463204153</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>30.7483380970101</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>32.34073287329842</v>
+        <v>33.22921454564179</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>25.60201663134832</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2492,7 +2492,7 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.47158305540374</v>
+        <v>18.73174619702914</v>
       </c>
       <c r="D13" t="n">
         <v>26.01631416254048</v>
@@ -2509,7 +2509,7 @@
         <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>19.35908298004286</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.0501923061036</v>
+        <v>15.40853021815369</v>
       </c>
       <c r="D15" t="n">
         <v>17.20021977840412</v>
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>14.46605242207675</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.16661937228147</v>
+        <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
         <v>10.86107485208246</v>
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>33.70830742531424</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.7014351913845</v>
+        <v>34.9050578767911</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>4.212679398923063</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.600649668549801</v>
+        <v>2.629120351972958</v>
       </c>
       <c r="C2" t="n">
-        <v>5.058945919983814</v>
+        <v>2.410190613925919</v>
       </c>
       <c r="D2" t="n">
-        <v>7.774460069930491</v>
+        <v>12.23748513343649</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.23105486786327</v>
+        <v>17.92180434102552</v>
       </c>
       <c r="C3" t="n">
-        <v>35.91233102134833</v>
+        <v>23.89083038284613</v>
       </c>
       <c r="D3" t="n">
-        <v>60.78000036992003</v>
+        <v>81.93175465791757</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.40226418349649</v>
+        <v>39.168788156335</v>
       </c>
       <c r="C4" t="n">
-        <v>111.7120895185403</v>
+        <v>95.03121427568276</v>
       </c>
       <c r="D4" t="n">
-        <v>126.2871159357884</v>
+        <v>151.4679628020149</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.82874359776711</v>
+        <v>39.19627709205391</v>
       </c>
       <c r="C5" t="n">
-        <v>237.1657016534233</v>
+        <v>198.2394051800372</v>
       </c>
       <c r="D5" t="n">
-        <v>107.6486357706628</v>
+        <v>113.4654909183251</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.36233132279187</v>
+        <v>31.23528495831652</v>
       </c>
       <c r="C6" t="n">
-        <v>261.2734982789079</v>
+        <v>216.755166882132</v>
       </c>
       <c r="D6" t="n">
-        <v>53.41394734495622</v>
+        <v>51.80388110999145</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.204465564390594</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>195.4100082963978</v>
+        <v>171.2158178729395</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>34.55457394637499</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.838633523605028</v>
+        <v>4.088979188187965</v>
       </c>
       <c r="C8" t="n">
-        <v>94.96445543179397</v>
+        <v>94.38031554776711</v>
       </c>
       <c r="D8" t="n">
-        <v>31.2097595180061</v>
+        <v>31.54355373745002</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>30.7296848906294</v>
+        <v>31.94999728700819</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>32.06093477758807</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>25.33890824661018</v>
+        <v>26.05067533218912</v>
       </c>
       <c r="D10" t="n">
-        <v>23.20360698987336</v>
+        <v>23.63066724122073</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>19.54659679155399</v>
+        <v>20.43507846389736</v>
       </c>
       <c r="D11" t="n">
-        <v>22.92282714645877</v>
+        <v>23.10052348092744</v>
       </c>
     </row>
     <row r="12">
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>14.97067074205961</v>
+        <v>15.18763698469816</v>
       </c>
       <c r="D12" t="n">
         <v>21.26269177857742</v>
@@ -2806,7 +2806,7 @@
         <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.59876828859932</v>
+        <v>12.90605532002857</v>
       </c>
       <c r="D14" t="n">
         <v>14.44249047717483</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>11.82515109765283</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -2845,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>11.98615772114931</v>
+        <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
         <v>9.092947236733956</v>
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.89283493598363</v>
+        <v>29.96293993361265</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>3.21031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.704714925199963</v>
+        <v>3.232895190084747</v>
       </c>
       <c r="C2" t="n">
-        <v>6.090762757147212</v>
+        <v>6.48542533425443</v>
       </c>
       <c r="D2" t="n">
-        <v>14.33940696822891</v>
+        <v>12.88052987971815</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.78864650614645</v>
+        <v>13.62174939642449</v>
       </c>
       <c r="C3" t="n">
-        <v>27.84236489243954</v>
+        <v>16.51299638543135</v>
       </c>
       <c r="D3" t="n">
-        <v>53.9863062565321</v>
+        <v>74.38702355078082</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.61999118966102</v>
+        <v>36.83321036793183</v>
       </c>
       <c r="C4" t="n">
-        <v>101.9996594804266</v>
+        <v>77.55905038320228</v>
       </c>
       <c r="D4" t="n">
-        <v>127.3208962683603</v>
+        <v>156.3177964609941</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.75635630956011</v>
+        <v>47.71293842639499</v>
       </c>
       <c r="C5" t="n">
-        <v>224.8447679651258</v>
+        <v>189.0109767601172</v>
       </c>
       <c r="D5" t="n">
-        <v>123.822929198129</v>
+        <v>135.6039016490907</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.57996051796516</v>
+        <v>40.05039759474864</v>
       </c>
       <c r="C6" t="n">
-        <v>312.9968760771512</v>
+        <v>262.642054578628</v>
       </c>
       <c r="D6" t="n">
-        <v>69.75611962984863</v>
+        <v>69.15234479173684</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.6066633279623</v>
+        <v>17.90609637775757</v>
       </c>
       <c r="C7" t="n">
-        <v>271.106683284644</v>
+        <v>235.2346039191698</v>
       </c>
       <c r="D7" t="n">
-        <v>39.82459562277186</v>
+        <v>39.94436884268997</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.090361846519712</v>
+        <v>5.507604620824606</v>
       </c>
       <c r="C8" t="n">
-        <v>160.2212253330794</v>
+        <v>148.4549790976814</v>
       </c>
       <c r="D8" t="n">
-        <v>33.04562772494764</v>
+        <v>33.29597338953057</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>60.23905738488002</v>
+        <v>63.01249464937726</v>
       </c>
       <c r="D9" t="n">
-        <v>32.17187226816797</v>
+        <v>32.8374972116473</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>30.03657101143117</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D10" t="n">
-        <v>24.48478774391545</v>
+        <v>24.76949457814703</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>22.92282714645877</v>
+        <v>23.98900515327081</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.14033316844506</v>
+        <v>17.35729941108361</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.08946221427348</v>
+        <v>15.34962535589888</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>13.82791641431633</v>
       </c>
       <c r="D14" t="n">
         <v>14.13520344574558</v>
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>13.25850274585317</v>
       </c>
       <c r="D15" t="n">
         <v>11.82515109765283</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.52766584773283</v>
+        <v>33.99988649347554</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.884955592153876</v>
+        <v>2.112721059539136</v>
       </c>
       <c r="C2" t="n">
-        <v>3.661918936840602</v>
+        <v>3.689407872559513</v>
       </c>
       <c r="D2" t="n">
-        <v>10.4801567428347</v>
+        <v>9.151852098988766</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.01659189998096</v>
+        <v>12.64981916922015</v>
       </c>
       <c r="C3" t="n">
-        <v>26.51209675318512</v>
+        <v>20.86704745376596</v>
       </c>
       <c r="D3" t="n">
-        <v>53.11745953827367</v>
+        <v>69.13958207158161</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.8422260237193</v>
+        <v>33.20859784385261</v>
       </c>
       <c r="C4" t="n">
-        <v>90.46216046011808</v>
+        <v>63.46900733185205</v>
       </c>
       <c r="D4" t="n">
-        <v>126.2998786559437</v>
+        <v>158.0407636819473</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>55.02695882303374</v>
+        <v>52.22897786593033</v>
       </c>
       <c r="C5" t="n">
-        <v>218.8806506618264</v>
+        <v>177.7945092390974</v>
       </c>
       <c r="D5" t="n">
-        <v>135.211202567392</v>
+        <v>153.0790107846839</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.85921883432777</v>
+        <v>46.89317909334891</v>
       </c>
       <c r="C6" t="n">
-        <v>342.3805848652582</v>
+        <v>288.2421077145678</v>
       </c>
       <c r="D6" t="n">
-        <v>80.50331174823846</v>
+        <v>82.8781594448115</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.69029180927252</v>
+        <v>16.70836417857646</v>
       </c>
       <c r="C7" t="n">
-        <v>333.4486442520206</v>
+        <v>289.3720993221558</v>
       </c>
       <c r="D7" t="n">
-        <v>44.37597797966008</v>
+        <v>45.45393695892307</v>
       </c>
     </row>
     <row r="8">
@@ -3352,10 +3352,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.088979188187965</v>
+        <v>4.506221962492859</v>
       </c>
       <c r="C8" t="n">
-        <v>206.7855189455057</v>
+        <v>191.8482276253905</v>
       </c>
       <c r="D8" t="n">
         <v>34.29735604786232</v>
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>67.00624431025328</v>
+        <v>73.44061876388687</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>32.61562223048752</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>30.89069151412589</v>
+        <v>31.8871654339364</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>25.33890824661018</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.38973814305275</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.48943444052943</v>
+        <v>16.92336692580652</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7439280801076</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.18701508989241</v>
+        <v>11.44717823151781</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
         <v>11.06233313145306</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.371321616383547</v>
+        <v>3.147483139815274</v>
       </c>
       <c r="C2" t="n">
-        <v>17.58899186928585</v>
+        <v>5.947427592327178</v>
       </c>
       <c r="D2" t="n">
-        <v>11.93608858823272</v>
+        <v>8.033641463851648</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.395325529641976</v>
+        <v>10.02364406035993</v>
       </c>
       <c r="C3" t="n">
-        <v>21.05848825609408</v>
+        <v>17.85799074024948</v>
       </c>
       <c r="D3" t="n">
-        <v>50.1378552558846</v>
+        <v>61.90901022980386</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.22662915542755</v>
+        <v>28.75440850968483</v>
       </c>
       <c r="C4" t="n">
-        <v>79.89462817160542</v>
+        <v>58.24905478837175</v>
       </c>
       <c r="D4" t="n">
-        <v>122.8284187737269</v>
+        <v>156.3560846214598</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.84886157793756</v>
+        <v>51.78719139901926</v>
       </c>
       <c r="C5" t="n">
-        <v>197.0613079349411</v>
+        <v>151.6063892283137</v>
       </c>
       <c r="D5" t="n">
-        <v>145.5686408471958</v>
+        <v>168.6887992822082</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>57.27810630887167</v>
+        <v>55.70829172978102</v>
       </c>
       <c r="C6" t="n">
-        <v>345.681220646936</v>
+        <v>287.0748096942183</v>
       </c>
       <c r="D6" t="n">
-        <v>97.08699396837559</v>
+        <v>102.8027291025005</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.7455727803466</v>
+        <v>29.58398531977338</v>
       </c>
       <c r="C7" t="n">
-        <v>395.3713989496839</v>
+        <v>341.1740169367388</v>
       </c>
       <c r="D7" t="n">
-        <v>52.76010337392783</v>
+        <v>53.65840252331367</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.844164156932015</v>
+        <v>8.595201150680824</v>
       </c>
       <c r="C8" t="n">
-        <v>292.5706333425919</v>
+        <v>268.2036553231861</v>
       </c>
       <c r="D8" t="n">
-        <v>36.88426124855267</v>
+        <v>37.63529824230147</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
         <v>132.7921762241278</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>33.50312215512664</v>
       </c>
     </row>
     <row r="10">
@@ -3691,10 +3691,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>46.83427423109409</v>
+        <v>50.39310965898878</v>
       </c>
       <c r="D10" t="n">
         <v>26.47773558353648</v>
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>27.72062817711293</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>24.87748682561417</v>
       </c>
     </row>
     <row r="12">
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.09302935219197</v>
+        <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
         <v>20.17786056538469</v>
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>12.74799393964483</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>11.67690719431156</v>
+      </c>
+      <c r="D14" t="n">
         <v>11.36962016288231</v>
-      </c>
-      <c r="D14" t="n">
-        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.86552592671396</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.494841900669398</v>
+        <v>5.564545987670921</v>
       </c>
       <c r="C2" t="n">
-        <v>7.303221171892022</v>
+        <v>5.867906028283186</v>
       </c>
       <c r="D2" t="n">
-        <v>21.09088593033422</v>
+        <v>7.191301933607885</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.462223242251</v>
+        <v>2.250165738133689</v>
       </c>
       <c r="C2" t="n">
-        <v>10.41241615124167</v>
+        <v>3.377212102609028</v>
       </c>
       <c r="D2" t="n">
-        <v>8.8799079849124</v>
+        <v>5.912084674974292</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.94925221901543</v>
+        <v>13.41067364001143</v>
       </c>
       <c r="C3" t="n">
-        <v>37.18369429834794</v>
+        <v>22.15313694632928</v>
       </c>
       <c r="D3" t="n">
-        <v>55.10058990085223</v>
+        <v>66.04216806468294</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.80241633620168</v>
+        <v>39.56443248114646</v>
       </c>
       <c r="C4" t="n">
-        <v>113.5754466612007</v>
+        <v>85.03800439415447</v>
       </c>
       <c r="D4" t="n">
-        <v>126.6444721001343</v>
+        <v>160.6443585936098</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.7658296292373</v>
+        <v>32.81491701444964</v>
       </c>
       <c r="C5" t="n">
-        <v>294.2297869627691</v>
+        <v>236.1839539491765</v>
       </c>
       <c r="D5" t="n">
-        <v>134.3767170187822</v>
+        <v>152.1708941582556</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>17.83148355223482</v>
+        <v>18.35475507859837</v>
       </c>
       <c r="C6" t="n">
-        <v>321.3692204989679</v>
+        <v>280.9565580013522</v>
       </c>
       <c r="D6" t="n">
-        <v>77.20267596656069</v>
+        <v>81.10708658635025</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.150248456478767</v>
+        <v>5.689227946110266</v>
       </c>
       <c r="C7" t="n">
-        <v>205.7105052093554</v>
+        <v>188.5829347610656</v>
       </c>
       <c r="D7" t="n">
-        <v>32.09922293805371</v>
+        <v>33.29695513723482</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.50207398749762</v>
+        <v>1.752419652080557</v>
       </c>
       <c r="C8" t="n">
         <v>97.88515485192822</v>
       </c>
       <c r="D8" t="n">
-        <v>24.11663235482289</v>
+        <v>24.61732368398877</v>
       </c>
     </row>
     <row r="9">
@@ -4299,10 +4299,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>35.72187196672443</v>
+        <v>38.38437174064178</v>
       </c>
       <c r="D9" t="n">
         <v>20.1906232855399</v>
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>20.92595231602077</v>
+        <v>21.6377194015997</v>
       </c>
       <c r="D10" t="n">
-        <v>18.93300447639974</v>
+        <v>19.50241814486289</v>
       </c>
     </row>
     <row r="11">
@@ -4330,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.28188476430585</v>
+        <v>15.81497376771187</v>
       </c>
       <c r="D11" t="n">
         <v>16.17036643664921</v>
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.41437964665016</v>
+        <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
-        <v>13.0179745583127</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>9.626036240139976</v>
+      </c>
+      <c r="D13" t="n">
         <v>9.365873098514571</v>
-      </c>
-      <c r="D13" t="n">
-        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.343071917138642</v>
+        <v>6.085854018625978</v>
       </c>
       <c r="C2" t="n">
-        <v>6.806456833543137</v>
+        <v>7.142214548395546</v>
       </c>
       <c r="D2" t="n">
-        <v>22.95424307299467</v>
+        <v>17.75098024048658</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.67298020349457</v>
+        <v>11.8202423591316</v>
       </c>
       <c r="C3" t="n">
-        <v>18.40286071610646</v>
+        <v>15.0207398749762</v>
       </c>
       <c r="D3" t="n">
-        <v>20.85232123820225</v>
+        <v>9.174432296186444</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.454950097693773</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
-        <v>9.449321653375552</v>
+        <v>9.424777960769381</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>8.130834486572086</v>
       </c>
       <c r="C6" t="n">
-        <v>18.43525839034661</v>
+        <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>32.52333794628834</v>
       </c>
     </row>
     <row r="7">
@@ -4585,10 +4585,10 @@
         <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>20.72076704583318</v>
+        <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>32.69808903764427</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.845546815263761</v>
+        <v>8.762098260402782</v>
       </c>
       <c r="C8" t="n">
         <v>21.69662426385451</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.764061755811273</v>
+        <v>8.874999246391162</v>
       </c>
       <c r="C9" t="n">
         <v>22.74218556887735</v>
       </c>
       <c r="D9" t="n">
-        <v>39.60468413702056</v>
+        <v>39.2718716652809</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>25.62361508084176</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>50.67781649322036</v>
       </c>
     </row>
     <row r="11">
@@ -4697,7 +4697,7 @@
         <v>5.375068680751286</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>26.15866757965626</v>
       </c>
       <c r="D15" t="n">
         <v>42.28387362191012</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39618835276138</v>
+        <v>13.39880544764168</v>
       </c>
       <c r="C21" t="n">
-        <v>70.1329860821037</v>
+        <v>70.14668734353586</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576022159148398</v>
+        <v>1.576330052663727</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.082908775513236</v>
+        <v>5.264131190171397</v>
       </c>
       <c r="C2" t="n">
-        <v>7.422994391810134</v>
+        <v>7.700828992111981</v>
       </c>
       <c r="D2" t="n">
-        <v>20.53718022513903</v>
+        <v>21.35792130588936</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.80890335503714</v>
+        <v>17.34748193404114</v>
       </c>
       <c r="C3" t="n">
-        <v>23.49322256262617</v>
+        <v>23.04652735719387</v>
       </c>
       <c r="D3" t="n">
-        <v>35.09257168830224</v>
+        <v>21.8684301120977</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>13.61782240560751</v>
+        <v>13.77097504747001</v>
       </c>
       <c r="C4" t="n">
-        <v>28.60125586782233</v>
+        <v>23.41959148480766</v>
       </c>
       <c r="D4" t="n">
-        <v>25.99766095615978</v>
+        <v>19.87155528165969</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.522330836388309</v>
+        <v>5.399612373357458</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>29.10881943091793</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.42267559664065</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>34.77743067523902</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
-        <v>24.37385025333556</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
-        <v>25.45180923259856</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
         <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
-        <v>40.60312155223957</v>
+        <v>40.27030908049991</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
-        <v>49.68134257340984</v>
+        <v>50.1084028247572</v>
       </c>
     </row>
     <row r="11">
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5025,7 +5025,7 @@
         <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>40.5049467818149</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43577311844927</v>
+        <v>15.44237686945025</v>
       </c>
       <c r="C21" t="n">
-        <v>86.11536581871698</v>
+        <v>86.1522077979856</v>
       </c>
       <c r="D21" t="n">
-        <v>3.24963644598932</v>
+        <v>3.251026709357947</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.978442608235575</v>
+        <v>4.300054944601029</v>
       </c>
       <c r="C2" t="n">
-        <v>10.94943214546467</v>
+        <v>6.953718989180158</v>
       </c>
       <c r="D2" t="n">
-        <v>21.48260326432871</v>
+        <v>24.701753986554</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.65949777754238</v>
+        <v>17.85308200172825</v>
       </c>
       <c r="C3" t="n">
-        <v>26.69372007847078</v>
+        <v>27.24349879284899</v>
       </c>
       <c r="D3" t="n">
-        <v>43.37852231214532</v>
+        <v>33.88011327355743</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.47438942979624</v>
+        <v>25.04045694451915</v>
       </c>
       <c r="C4" t="n">
-        <v>45.80540263704343</v>
+        <v>43.59745205019236</v>
       </c>
       <c r="D4" t="n">
-        <v>37.72660077879643</v>
+        <v>26.36777984066083</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>12.00186568441726</v>
+        <v>12.12458414744811</v>
       </c>
       <c r="C5" t="n">
-        <v>32.47130531796326</v>
+        <v>26.97351817418112</v>
       </c>
       <c r="D5" t="n">
-        <v>31.98043146583985</v>
+        <v>29.59969328304134</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.31700669748049</v>
+        <v>12.11574841810989</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>36.6290068454485</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.37385025333556</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>37.42913122440964</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.37389131106456</v>
+        <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>38.55323234577224</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>9.984374152190059</v>
       </c>
       <c r="C9" t="n">
-        <v>29.62030998483051</v>
+        <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.49062147687869</v>
+        <v>41.26874649571891</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>9.537678946757763</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>29.46715734296802</v>
       </c>
       <c r="D10" t="n">
-        <v>48.9695754878309</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5263,10 +5263,10 @@
         <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
-        <v>49.57727731675966</v>
+        <v>49.75497365122833</v>
       </c>
     </row>
     <row r="12">
@@ -5277,7 +5277,7 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.46010518258904</v>
+        <v>32.11100391050467</v>
       </c>
       <c r="D12" t="n">
         <v>46.2138096820101</v>
@@ -5291,7 +5291,7 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5305,7 +5305,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
         <v>45.47848065152925</v>
@@ -5316,7 +5316,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>27.5920192278566</v>
@@ -5333,10 +5333,10 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5350,7 +5350,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72461288220887</v>
+        <v>16.73625141340154</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0201385814741</v>
+        <v>102.0911336217494</v>
       </c>
       <c r="D21" t="n">
-        <v>4.181153220552217</v>
+        <v>5.020875424020461</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.983752257384309</v>
+        <v>4.314781160164732</v>
       </c>
       <c r="C2" t="n">
-        <v>11.96161402854314</v>
+        <v>6.068182559949535</v>
       </c>
       <c r="D2" t="n">
-        <v>18.27523351455438</v>
+        <v>26.9921713805618</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.20160243673586</v>
+        <v>16.1448409963388</v>
       </c>
       <c r="C3" t="n">
-        <v>35.61780671007428</v>
+        <v>27.08151042164826</v>
       </c>
       <c r="D3" t="n">
-        <v>50.05440670102362</v>
+        <v>45.11621574866217</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.95785126864217</v>
+        <v>30.31146036862027</v>
       </c>
       <c r="C4" t="n">
-        <v>56.87068101160924</v>
+        <v>57.33013893719674</v>
       </c>
       <c r="D4" t="n">
-        <v>50.25959197121121</v>
+        <v>36.82044764777662</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.08365384350601</v>
+        <v>24.71549845441346</v>
       </c>
       <c r="C5" t="n">
-        <v>60.62292073724056</v>
+        <v>55.61600744558182</v>
       </c>
       <c r="D5" t="n">
-        <v>37.69911184307752</v>
+        <v>32.05406254365837</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.98870205363455</v>
+        <v>11.27046364475338</v>
       </c>
       <c r="C6" t="n">
-        <v>32.60384125803657</v>
+        <v>28.29691407950582</v>
       </c>
       <c r="D6" t="n">
-        <v>38.76234460677682</v>
+        <v>38.15856976866503</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>8.563785224144926</v>
       </c>
       <c r="C7" t="n">
-        <v>21.13997331554657</v>
+        <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>39.52516257297658</v>
+        <v>39.46527596301753</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
         <v>31.54355373745002</v>
       </c>
       <c r="D8" t="n">
-        <v>39.8884092235479</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>34.39062207976576</v>
       </c>
       <c r="D9" t="n">
-        <v>42.3781214015178</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.82238578098934</v>
+        <v>10.10709261522091</v>
       </c>
       <c r="C10" t="n">
-        <v>33.02599277086271</v>
+        <v>33.31069960509428</v>
       </c>
       <c r="D10" t="n">
-        <v>48.54251523648354</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5574,10 +5574,10 @@
         <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>33.22921454564179</v>
       </c>
       <c r="D11" t="n">
-        <v>50.6434553235717</v>
+        <v>50.82115165804038</v>
       </c>
     </row>
     <row r="12">
@@ -5588,7 +5588,7 @@
         <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.49763257952867</v>
       </c>
       <c r="D12" t="n">
         <v>47.08167465256428</v>
@@ -5602,7 +5602,7 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>32.5203927031756</v>
+        <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5616,10 +5616,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5633,7 +5633,7 @@
         <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>41.74489413227862</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5661,7 +5661,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5686,7 +5686,7 @@
         <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.04309872256792</v>
+        <v>18.06175181081399</v>
       </c>
       <c r="C21" t="n">
-        <v>117.709739285324</v>
+        <v>117.8314284800722</v>
       </c>
       <c r="D21" t="n">
-        <v>6.014366240855973</v>
+        <v>6.880667356500569</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.35583463729385</v>
+        <v>4.991205328390784</v>
       </c>
       <c r="C2" t="n">
-        <v>12.67828985264331</v>
+        <v>7.045021525675111</v>
       </c>
       <c r="D2" t="n">
-        <v>19.17844140246144</v>
+        <v>32.24353985057799</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.24439842509522</v>
+        <v>13.6806542586793</v>
       </c>
       <c r="C3" t="n">
-        <v>39.13246349127786</v>
+        <v>23.54721868635975</v>
       </c>
       <c r="D3" t="n">
-        <v>49.68625131193107</v>
+        <v>52.30260894374882</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.28745645536184</v>
+        <v>22.29647211114931</v>
       </c>
       <c r="C4" t="n">
-        <v>61.92471819307181</v>
+        <v>52.86318688287376</v>
       </c>
       <c r="D4" t="n">
-        <v>55.19876467127691</v>
+        <v>43.9675709346934</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.21204180858409</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="C5" t="n">
-        <v>62.73367830137119</v>
+        <v>60.96653243372694</v>
       </c>
       <c r="D5" t="n">
-        <v>37.5518496874405</v>
+        <v>30.33600406122645</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.27675504160637</v>
+        <v>12.15600007398401</v>
       </c>
       <c r="C6" t="n">
-        <v>44.1560664939088</v>
+        <v>40.41266249761571</v>
       </c>
       <c r="D6" t="n">
-        <v>32.48308629041422</v>
+        <v>30.91327171132357</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.389794896314989</v>
+        <v>5.509568116233099</v>
       </c>
       <c r="C7" t="n">
-        <v>21.73883941513712</v>
+        <v>19.94224111636546</v>
       </c>
       <c r="D7" t="n">
-        <v>30.84160412891355</v>
+        <v>30.72183090899544</v>
       </c>
     </row>
     <row r="8">
@@ -5846,7 +5846,7 @@
         <v>18.60902773399829</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.74374815365835</v>
+        <v>22.07656062539802</v>
       </c>
       <c r="D9" t="n">
-        <v>30.39687241888974</v>
+        <v>29.95312245657017</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
         <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>33.02599277086271</v>
+        <v>33.73775985644164</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>34.47308888692249</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>31.67707142522758</v>
+        <v>32.11100391050467</v>
       </c>
     </row>
     <row r="13">
@@ -5913,7 +5913,7 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
         <v>30.43908757017236</v>
@@ -5941,10 +5941,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -5969,7 +5969,7 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
         <v>23.61103228713579</v>
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -5997,7 +5997,7 @@
         <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>15.64709491028566</v>
@@ -6011,7 +6011,7 @@
         <v>1.34499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.08745766113597</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.048591643635808</v>
+        <v>7.058844473218861</v>
       </c>
       <c r="C21" t="n">
-        <v>66.0805466590857</v>
+        <v>66.17666693642681</v>
       </c>
       <c r="D21" t="n">
-        <v>4.40536977727238</v>
+        <v>5.294133354914146</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.307328089158257</v>
+        <v>4.946044933995431</v>
       </c>
       <c r="C2" t="n">
-        <v>8.72577359534565</v>
+        <v>8.294786353181301</v>
       </c>
       <c r="D2" t="n">
-        <v>21.44136986075034</v>
+        <v>27.89047052994763</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.2681813541754</v>
+        <v>16.05648370295658</v>
       </c>
       <c r="C3" t="n">
-        <v>45.71508184825273</v>
+        <v>26.11448893296516</v>
       </c>
       <c r="D3" t="n">
-        <v>53.78995671568274</v>
+        <v>66.74902641174064</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.2093586073786</v>
+        <v>25.35952494839936</v>
       </c>
       <c r="C4" t="n">
-        <v>84.336054785618</v>
+        <v>56.80686741083319</v>
       </c>
       <c r="D4" t="n">
-        <v>68.43370547222817</v>
+        <v>60.75054793879262</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.36054775383262</v>
+        <v>28.83883881225006</v>
       </c>
       <c r="C5" t="n">
-        <v>93.87962421860125</v>
+        <v>83.52218593879741</v>
       </c>
       <c r="D5" t="n">
-        <v>49.21010367537139</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22.50067563363265</v>
+        <v>21.93715245139498</v>
       </c>
       <c r="C6" t="n">
-        <v>75.87437132271475</v>
+        <v>73.258013690897</v>
       </c>
       <c r="D6" t="n">
-        <v>37.59504658642736</v>
+        <v>34.05290086950487</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.65981657271187</v>
+        <v>10.71970318267092</v>
       </c>
       <c r="C7" t="n">
-        <v>46.23246288839079</v>
+        <v>42.75903951076558</v>
       </c>
       <c r="D7" t="n">
-        <v>33.77604801690726</v>
+        <v>32.93763547748049</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.591053175685585</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>24.86766934857171</v>
+        <v>23.61594102565702</v>
       </c>
       <c r="D8" t="n">
-        <v>31.71045084717197</v>
+        <v>32.3780392860598</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.18593553119691</v>
+        <v>23.40781051235669</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>31.17343485294896</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>4.840016181936776</v>
       </c>
       <c r="C10" t="n">
-        <v>24.48478774391545</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>33.31069960509428</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -6224,10 +6224,10 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>30.69925071179776</v>
+        <v>31.21957699504857</v>
       </c>
     </row>
     <row r="14">
@@ -6235,7 +6235,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
         <v>19.35908298004286</v>
@@ -6280,7 +6280,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6322,7 +6322,7 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.266105485797802</v>
+        <v>7.28081560192251</v>
       </c>
       <c r="C21" t="n">
-        <v>75.38584441515221</v>
+        <v>75.53846186994605</v>
       </c>
       <c r="D21" t="n">
-        <v>5.449579114348351</v>
+        <v>6.370713651682196</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.404521111878692</v>
+        <v>4.039891802975625</v>
       </c>
       <c r="C2" t="n">
-        <v>6.014186436215961</v>
+        <v>8.300676839406782</v>
       </c>
       <c r="D2" t="n">
-        <v>23.13193940746335</v>
+        <v>27.32498385230147</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.16862392541897</v>
+        <v>16.67007601811084</v>
       </c>
       <c r="C3" t="n">
-        <v>38.76430810218531</v>
+        <v>29.85003894762427</v>
       </c>
       <c r="D3" t="n">
-        <v>58.11946409141117</v>
+        <v>73.57217295625597</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.4420738710141</v>
+        <v>28.8692729910817</v>
       </c>
       <c r="C4" t="n">
-        <v>100.6595738641297</v>
+        <v>61.89919275276139</v>
       </c>
       <c r="D4" t="n">
-        <v>78.72045791732624</v>
+        <v>80.55828961967627</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.18998569520093</v>
+        <v>33.89483948912113</v>
       </c>
       <c r="C5" t="n">
-        <v>128.6334929489384</v>
+        <v>95.84311962709488</v>
       </c>
       <c r="D5" t="n">
-        <v>62.73367830137119</v>
+        <v>52.64622064023522</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.52333794628834</v>
+        <v>31.43654323768712</v>
       </c>
       <c r="C6" t="n">
-        <v>115.4820007028481</v>
+        <v>105.33858342257</v>
       </c>
       <c r="D6" t="n">
-        <v>44.1560664939088</v>
+        <v>39.40637110076273</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.98405535702057</v>
+        <v>18.86428213710246</v>
       </c>
       <c r="C7" t="n">
-        <v>80.12828412521617</v>
+        <v>77.792706336813</v>
       </c>
       <c r="D7" t="n">
-        <v>37.30935800449154</v>
+        <v>35.39298648580176</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.845546815263761</v>
+        <v>9.012443924985718</v>
       </c>
       <c r="C8" t="n">
-        <v>43.97738841173587</v>
+        <v>41.8911745402114</v>
       </c>
       <c r="D8" t="n">
-        <v>33.88011327355743</v>
+        <v>34.38080460272329</v>
       </c>
     </row>
     <row r="9">
@@ -6479,7 +6479,7 @@
         <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>27.84531013555227</v>
+        <v>27.29062268265283</v>
       </c>
       <c r="D9" t="n">
         <v>32.72655972106742</v>
@@ -6493,10 +6493,10 @@
         <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>26.76244241776806</v>
+        <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>34.30717352490479</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.264712027248144</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -6521,7 +6521,7 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
         <v>34.06370009425158</v>
@@ -6535,7 +6535,7 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
         <v>31.47974013667398</v>
@@ -6552,7 +6552,7 @@
         <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6591,7 +6591,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -6608,7 +6608,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6619,10 +6619,10 @@
         <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6630,10 +6630,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.468718114038479</v>
+        <v>7.490113827687003</v>
       </c>
       <c r="C21" t="n">
-        <v>84.02307878293288</v>
+        <v>84.26378056147878</v>
       </c>
       <c r="D21" t="n">
-        <v>6.535128349783669</v>
+        <v>7.490113827687003</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_53_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_53_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497639000846</v>
+        <v>10.84497644374073</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907214328928</v>
+        <v>37.78907233051815</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.101561981893926</v>
+        <v>0.8344855486097887</v>
       </c>
       <c r="C2" t="n">
-        <v>7.35918079103409</v>
+        <v>2.515237618280328</v>
       </c>
       <c r="D2" t="n">
-        <v>23.18397203578843</v>
+        <v>10.13752679405256</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.07964473723101</v>
+        <v>7.574183538264141</v>
       </c>
       <c r="C3" t="n">
-        <v>31.10667600906019</v>
+        <v>36.00559705325177</v>
       </c>
       <c r="D3" t="n">
-        <v>77.58752106662543</v>
+        <v>54.3593703841459</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.38803668955152</v>
+        <v>14.76646721957627</v>
       </c>
       <c r="C4" t="n">
-        <v>68.15292562881358</v>
+        <v>119.3186707310446</v>
       </c>
       <c r="D4" t="n">
-        <v>96.46063893306611</v>
+        <v>77.91640654754811</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.97538385859838</v>
+        <v>14.62804079327748</v>
       </c>
       <c r="C5" t="n">
-        <v>105.6360529769568</v>
+        <v>144.0223882130071</v>
       </c>
       <c r="D5" t="n">
-        <v>68.69779560467057</v>
+        <v>51.39449231732053</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.68184129502858</v>
+        <v>9.338384162795663</v>
       </c>
       <c r="C6" t="n">
-        <v>129.5700802587898</v>
+        <v>98.73731185921449</v>
       </c>
       <c r="D6" t="n">
-        <v>46.12839763174064</v>
+        <v>30.59125846433062</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.14670668075605</v>
+        <v>5.569454726192155</v>
       </c>
       <c r="C7" t="n">
-        <v>114.8625179014683</v>
+        <v>51.98157744446011</v>
       </c>
       <c r="D7" t="n">
-        <v>38.86640986342697</v>
+        <v>28.98511922018283</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.85384276525424</v>
+        <v>6.091744504851458</v>
       </c>
       <c r="C8" t="n">
-        <v>73.1009340582175</v>
+        <v>30.45872252425729</v>
       </c>
       <c r="D8" t="n">
-        <v>35.9663271450819</v>
+        <v>31.12631096314512</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.432811868852599</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>39.71562162760046</v>
+        <v>30.95155987178918</v>
       </c>
       <c r="D9" t="n">
-        <v>34.39062207976576</v>
+        <v>35.16718451382499</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>3.4164820107789</v>
       </c>
       <c r="C10" t="n">
-        <v>30.46363126277853</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>37.5813021185679</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>30.74146586308036</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>37.49392657288993</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.55471281509523</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>37.75212621910684</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>19.77239876353076</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>36.16267668593127</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.35381438862312</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>27.04125876577415</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>25.44199175555609</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
+        <v>24.55547357862122</v>
+      </c>
+      <c r="D17" t="n">
         <v>17.9443845382232</v>
-      </c>
-      <c r="D17" t="n">
-        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>26.21757244191107</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>11.23610247510475</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>10.83260416865931</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>84.25358797846125</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.684994079856874</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>93.18055321826459</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.645618339838983</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.285148802588081</v>
+        <v>1.392118244621977</v>
       </c>
       <c r="C2" t="n">
-        <v>7.015569094547707</v>
+        <v>14.26283064729766</v>
       </c>
       <c r="D2" t="n">
-        <v>29.21975692149782</v>
+        <v>11.56007921750619</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.82853830912208</v>
+        <v>5.114905539125882</v>
       </c>
       <c r="C3" t="n">
-        <v>29.64878066825367</v>
+        <v>20.94067853158447</v>
       </c>
       <c r="D3" t="n">
-        <v>77.58261232810419</v>
+        <v>49.97095814616264</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.22662915542755</v>
+        <v>14.71541633895544</v>
       </c>
       <c r="C4" t="n">
-        <v>72.8368439257751</v>
+        <v>104.1565591866568</v>
       </c>
       <c r="D4" t="n">
-        <v>110.7038346262788</v>
+        <v>87.10556505929826</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.87153958612647</v>
+        <v>18.62866268808323</v>
       </c>
       <c r="C5" t="n">
-        <v>114.1281706186917</v>
+        <v>184.4949373205819</v>
       </c>
       <c r="D5" t="n">
-        <v>83.89034132788996</v>
+        <v>66.83247496660162</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.16235789076178</v>
+        <v>14.12833121181585</v>
       </c>
       <c r="C6" t="n">
-        <v>148.0053386491364</v>
+        <v>165.9575771689936</v>
       </c>
       <c r="D6" t="n">
-        <v>55.70829172978102</v>
+        <v>38.9233512302733</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>36.83026512481909</v>
+        <v>8.084692344472483</v>
       </c>
       <c r="C7" t="n">
-        <v>148.039699818785</v>
+        <v>97.07619474362885</v>
       </c>
       <c r="D7" t="n">
-        <v>42.4596064609703</v>
+        <v>31.56024344842221</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21.94696992843745</v>
+        <v>6.342090169434394</v>
       </c>
       <c r="C8" t="n">
-        <v>110.485886635936</v>
+        <v>49.23464736797754</v>
       </c>
       <c r="D8" t="n">
-        <v>38.21943812632832</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -1189,10 +1189,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.87187407682917</v>
+        <v>6.212499472473814</v>
       </c>
       <c r="C9" t="n">
-        <v>62.90155715879737</v>
+        <v>35.38905949498476</v>
       </c>
       <c r="D9" t="n">
         <v>35.49999698556465</v>
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.405903770210439</v>
+        <v>4.128249096357838</v>
       </c>
       <c r="C10" t="n">
-        <v>38.57777603837842</v>
+        <v>34.02246669067321</v>
       </c>
       <c r="D10" t="n">
-        <v>35.87306111317846</v>
+        <v>38.43542262126263</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>32.34073287329842</v>
+        <v>33.40691088011046</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>38.38240824523329</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>30.59224021203486</v>
+        <v>28.42257778564941</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>38.18605870438393</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>27.83745615391831</v>
+        <v>22.63419332141022</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>36.94316611080748</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>28.5776939229204</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>25.083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>26.44435616159209</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>16.99994324673777</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>8.560839981032187</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>50.2949348885641</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>9.095892479846698</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>45.7376620454504</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.864929290832857</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>101.260964619473</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.83116161354107</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.476589604916207</v>
+        <v>0.7461282552275759</v>
       </c>
       <c r="C2" t="n">
-        <v>10.10709261522091</v>
+        <v>6.065237316836795</v>
       </c>
       <c r="D2" t="n">
-        <v>30.17303394232147</v>
+        <v>7.907977757708058</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.96736564604837</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C3" t="n">
-        <v>28.27924262082937</v>
+        <v>39.07355862902305</v>
       </c>
       <c r="D3" t="n">
-        <v>80.83710596768236</v>
+        <v>49.62734644967627</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.69434197327653</v>
+        <v>16.0044510746315</v>
       </c>
       <c r="C4" t="n">
-        <v>72.45396232111885</v>
+        <v>93.37206065550565</v>
       </c>
       <c r="D4" t="n">
-        <v>119.3697216116654</v>
+        <v>93.1550944128671</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.85328729037328</v>
+        <v>18.57957530287089</v>
       </c>
       <c r="C5" t="n">
-        <v>121.6139968635737</v>
+        <v>212.3029410433728</v>
       </c>
       <c r="D5" t="n">
-        <v>99.10743074371554</v>
+        <v>74.26921382627121</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.71079500453725</v>
+        <v>11.27046364475338</v>
       </c>
       <c r="C6" t="n">
-        <v>162.8179480108123</v>
+        <v>207.9400542457</v>
       </c>
       <c r="D6" t="n">
-        <v>66.73724543928969</v>
+        <v>39.48687441251096</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>43.89688509998763</v>
+        <v>4.19206269713388</v>
       </c>
       <c r="C7" t="n">
-        <v>175.4677671800324</v>
+        <v>90.9677605278052</v>
       </c>
       <c r="D7" t="n">
-        <v>47.13076203777662</v>
+        <v>33.23706852727577</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>29.37389131106456</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>146.8694565553228</v>
+        <v>42.89255719854314</v>
       </c>
       <c r="D8" t="n">
-        <v>40.63944621729671</v>
+        <v>36.21667280966483</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15.53124868118453</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>94.96249193638545</v>
+        <v>25.95937279569415</v>
       </c>
       <c r="D9" t="n">
-        <v>36.72030938194344</v>
+        <v>40.04843409934012</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.114144775599888</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>53.38253141842032</v>
+        <v>26.1930287493049</v>
       </c>
       <c r="D10" t="n">
-        <v>36.72718161587318</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>37.49392657288993</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>30.56376952861169</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>33.62976760897449</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D12" t="n">
-        <v>36.23336252063703</v>
+        <v>30.15830772675777</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
-        <v>31.65056423721292</v>
+        <v>20.89551813718911</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>43.44429940832985</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>7.555530331883453</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>39.59388491227386</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.028992063779381</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>109.3950168689941</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11.03986408769665</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.028912651779663</v>
+        <v>0.5213080309550563</v>
       </c>
       <c r="C2" t="n">
-        <v>6.872233929727672</v>
+        <v>7.764642592888023</v>
       </c>
       <c r="D2" t="n">
-        <v>24.91381149067131</v>
+        <v>7.047966768787852</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.01569226773472</v>
+        <v>3.966260725157114</v>
       </c>
       <c r="C3" t="n">
-        <v>44.71369918992098</v>
+        <v>30.35563901531138</v>
       </c>
       <c r="D3" t="n">
-        <v>87.82714962191966</v>
+        <v>44.75787783661209</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.58626761035137</v>
+        <v>13.464669763745</v>
       </c>
       <c r="C4" t="n">
-        <v>100.3532685804047</v>
+        <v>96.57550341446299</v>
       </c>
       <c r="D4" t="n">
-        <v>113.5371585007351</v>
+        <v>96.51168981368694</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.00435326364027</v>
+        <v>21.3775562599743</v>
       </c>
       <c r="C5" t="n">
-        <v>97.29119749085893</v>
+        <v>193.8706278961389</v>
       </c>
       <c r="D5" t="n">
-        <v>66.51340696272142</v>
+        <v>89.82991493858316</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.25037102677872</v>
+        <v>17.10695374650067</v>
       </c>
       <c r="C6" t="n">
-        <v>115.5625040145963</v>
+        <v>274.5565447173673</v>
       </c>
       <c r="D6" t="n">
-        <v>31.03402667894593</v>
+        <v>50.79758971313847</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.46314823669301</v>
+        <v>7.545712854840985</v>
       </c>
       <c r="C7" t="n">
-        <v>103.2445155694116</v>
+        <v>186.8462230722529</v>
       </c>
       <c r="D7" t="n">
-        <v>28.56591295046944</v>
+        <v>36.71049190490098</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>4.506221962492859</v>
       </c>
       <c r="C8" t="n">
-        <v>69.9298889735003</v>
+        <v>76.52232480751763</v>
       </c>
       <c r="D8" t="n">
-        <v>27.03733177495716</v>
+        <v>37.38495257771854</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>3.217187226816797</v>
       </c>
       <c r="C9" t="n">
-        <v>40.71405904281946</v>
+        <v>37.60780930658255</v>
       </c>
       <c r="D9" t="n">
-        <v>27.95624762613216</v>
+        <v>40.82499653339935</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
         <v>29.32480392585223</v>
       </c>
       <c r="D10" t="n">
-        <v>28.61303684027329</v>
+        <v>31.8871654339364</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>28.96450251839364</v>
+        <v>31.62994753542373</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>21.26269177857742</v>
       </c>
       <c r="D12" t="n">
-        <v>26.68684784454105</v>
+        <v>30.8092064546734</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>20.28094407433061</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>23.66110142005238</v>
+        <v>20.58823110575986</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>37.19842051391164</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.39947350463721</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>46.74984392852887</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>73.30219233758808</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.677626900108552</v>
+        <v>0.3347759671481623</v>
       </c>
       <c r="C2" t="n">
-        <v>3.468514639103981</v>
+        <v>4.458116324984766</v>
       </c>
       <c r="D2" t="n">
-        <v>18.63749841742145</v>
+        <v>5.370159942230052</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.02550974477719</v>
+        <v>3.043417883165112</v>
       </c>
       <c r="C3" t="n">
-        <v>36.33939127269569</v>
+        <v>30.65998080362789</v>
       </c>
       <c r="D3" t="n">
-        <v>87.76333602114362</v>
+        <v>41.03214529899544</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.72437524148068</v>
+        <v>11.47368541953247</v>
       </c>
       <c r="C4" t="n">
-        <v>108.4831213192725</v>
+        <v>89.37732924692536</v>
       </c>
       <c r="D4" t="n">
-        <v>129.8989657397125</v>
+        <v>97.3540293439307</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.92505268377453</v>
+        <v>22.31021657900877</v>
       </c>
       <c r="C5" t="n">
-        <v>139.4327176956533</v>
+        <v>193.9933463591698</v>
       </c>
       <c r="D5" t="n">
-        <v>84.70028318389357</v>
+        <v>100.7518581483289</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.00006641992479</v>
+        <v>20.7296027751714</v>
       </c>
       <c r="C6" t="n">
-        <v>137.7814180571101</v>
+        <v>303.5779886026073</v>
       </c>
       <c r="D6" t="n">
-        <v>39.04410619789565</v>
+        <v>60.41773546705297</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.38518925743002</v>
+        <v>8.024805734513427</v>
       </c>
       <c r="C7" t="n">
-        <v>129.4149641215188</v>
+        <v>260.386980101973</v>
       </c>
       <c r="D7" t="n">
-        <v>31.14103717870882</v>
+        <v>40.96244121199391</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.012443924985718</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>92.79479300540851</v>
+        <v>117.9962565734241</v>
       </c>
       <c r="D8" t="n">
-        <v>28.28906009787184</v>
+        <v>39.30426933952106</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.659374604355361</v>
+        <v>2.662499773917349</v>
       </c>
       <c r="C9" t="n">
-        <v>45.70624611891449</v>
+        <v>48.25780840225195</v>
       </c>
       <c r="D9" t="n">
-        <v>28.84374755077128</v>
+        <v>40.93593402397924</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>32.17187226816798</v>
+        <v>31.8871654339364</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>32.88363935374691</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>32.87382187670443</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>21.04572553593887</v>
+        <v>22.78145547704723</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>29.29044275620359</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>16.59349969717959</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>31.53373626040754</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>40.09163099832699</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>63.79200232654924</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.462043315801753</v>
+        <v>0.8727737090754144</v>
       </c>
       <c r="C2" t="n">
-        <v>5.055018929166827</v>
+        <v>10.88856378780137</v>
       </c>
       <c r="D2" t="n">
-        <v>17.54088623177776</v>
+        <v>8.626617077216721</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.39656931925348</v>
+        <v>2.115666302651876</v>
       </c>
       <c r="C3" t="n">
-        <v>24.30807315715103</v>
+        <v>24.04300127700439</v>
       </c>
       <c r="D3" t="n">
-        <v>83.34547135203297</v>
+        <v>36.52101459798134</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.4420738710141</v>
+        <v>8.780751466783471</v>
       </c>
       <c r="C4" t="n">
-        <v>99.37053912845366</v>
+        <v>83.05978277009714</v>
       </c>
       <c r="D4" t="n">
-        <v>141.985261726695</v>
+        <v>95.82250292530568</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.25732537616646</v>
+        <v>20.54307071136451</v>
       </c>
       <c r="C5" t="n">
-        <v>169.0569546713008</v>
+        <v>180.1752474218959</v>
       </c>
       <c r="D5" t="n">
-        <v>107.4768299224196</v>
+        <v>109.1703447122453</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.95102009244145</v>
+        <v>24.67426505083509</v>
       </c>
       <c r="C6" t="n">
-        <v>178.7576037369635</v>
+        <v>309.897498574844</v>
       </c>
       <c r="D6" t="n">
-        <v>52.89067581859268</v>
+        <v>74.7070733023653</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.11056194214817</v>
+        <v>14.13323995033708</v>
       </c>
       <c r="C7" t="n">
-        <v>163.191012138426</v>
+        <v>337.101727459523</v>
       </c>
       <c r="D7" t="n">
-        <v>34.49468733641593</v>
+        <v>47.25053525769474</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.18487166803466</v>
+        <v>5.841398840268521</v>
       </c>
       <c r="C8" t="n">
-        <v>128.7611201504904</v>
+        <v>212.6269177857742</v>
       </c>
       <c r="D8" t="n">
-        <v>29.87458264023044</v>
+        <v>41.47393176590651</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.990624491314035</v>
+        <v>3.217187226816797</v>
       </c>
       <c r="C9" t="n">
-        <v>74.99374363200533</v>
+        <v>86.97499261463339</v>
       </c>
       <c r="D9" t="n">
-        <v>29.50937249425062</v>
+        <v>41.71249645803847</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>1.70824100538945</v>
       </c>
       <c r="C10" t="n">
         <v>41.85190463204153</v>
       </c>
       <c r="D10" t="n">
-        <v>30.7483380970101</v>
+        <v>34.44952694202058</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>31.09685853201771</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>33.40691088011046</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
         <v>25.60201663134832</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>24.45533531278805</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>17.20807376003809</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.5083653843506</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>32.6087499965578</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.0334615374024</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.46605242207675</v>
+        <v>39.67831521483909</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.9050578767911</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.629120351972958</v>
+        <v>0.5998478472948011</v>
       </c>
       <c r="C2" t="n">
-        <v>2.410190613925919</v>
+        <v>5.922883899721008</v>
       </c>
       <c r="D2" t="n">
-        <v>12.23748513343649</v>
+        <v>6.279258316362599</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.92180434102552</v>
+        <v>3.293763547748048</v>
       </c>
       <c r="C3" t="n">
-        <v>23.89083038284613</v>
+        <v>33.78684724165398</v>
       </c>
       <c r="D3" t="n">
-        <v>81.93175465791757</v>
+        <v>40.28601704376786</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.168788156335</v>
+        <v>14.23043297305752</v>
       </c>
       <c r="C4" t="n">
-        <v>95.03121427568276</v>
+        <v>114.2135826689612</v>
       </c>
       <c r="D4" t="n">
-        <v>151.4679628020149</v>
+        <v>99.54921721062658</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.19627709205391</v>
+        <v>14.84893402673301</v>
       </c>
       <c r="C5" t="n">
-        <v>198.2394051800372</v>
+        <v>265.3909481505191</v>
       </c>
       <c r="D5" t="n">
-        <v>113.4654909183251</v>
+        <v>101.5127126191202</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.23528495831652</v>
+        <v>8.774860980557992</v>
       </c>
       <c r="C6" t="n">
-        <v>216.755166882132</v>
+        <v>291.8647567432386</v>
       </c>
       <c r="D6" t="n">
-        <v>51.80388110999145</v>
+        <v>64.08063615159783</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>3.832743037379548</v>
       </c>
       <c r="C7" t="n">
-        <v>171.2158178729395</v>
+        <v>149.5368650677614</v>
       </c>
       <c r="D7" t="n">
-        <v>34.55457394637499</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.088979188187965</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C8" t="n">
-        <v>94.38031554776711</v>
+        <v>64.08849013323177</v>
       </c>
       <c r="D8" t="n">
-        <v>31.54355373745002</v>
+        <v>30.70906818884022</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.220312396378785</v>
       </c>
       <c r="C9" t="n">
         <v>31.94999728700819</v>
       </c>
       <c r="D9" t="n">
-        <v>32.06093477758807</v>
+        <v>26.29218526743382</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>26.05067533218912</v>
+        <v>24.34243432679967</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>26.1930287493049</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
         <v>20.43507846389736</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.18763698469816</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>14.04880964777186</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>12.90605532002857</v>
+        <v>27.3485457972034</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>8.296749848589794</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.18348900970292</v>
+        <v>33.68376373270807</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>28.80545939030567</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.96293993361265</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.232895190084747</v>
+        <v>0.2994330497952772</v>
       </c>
       <c r="C2" t="n">
-        <v>6.48542533425443</v>
+        <v>3.181844309463912</v>
       </c>
       <c r="D2" t="n">
-        <v>12.88052987971815</v>
+        <v>4.57690779719863</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.62174939642449</v>
+        <v>2.68998870963626</v>
       </c>
       <c r="C3" t="n">
-        <v>16.51299638543135</v>
+        <v>28.11234551110741</v>
       </c>
       <c r="D3" t="n">
-        <v>74.38702355078082</v>
+        <v>36.24612524079224</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.83321036793183</v>
+        <v>9.737955478424112</v>
       </c>
       <c r="C4" t="n">
-        <v>77.55905038320228</v>
+        <v>95.92460468654734</v>
       </c>
       <c r="D4" t="n">
-        <v>156.3177964609941</v>
+        <v>93.39758609581605</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.71293842639499</v>
+        <v>14.08807955594173</v>
       </c>
       <c r="C5" t="n">
-        <v>189.0109767601172</v>
+        <v>214.5855044557466</v>
       </c>
       <c r="D5" t="n">
-        <v>135.6039016490907</v>
+        <v>101.2181883078462</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.05039759474864</v>
+        <v>8.45284773356504</v>
       </c>
       <c r="C6" t="n">
-        <v>262.642054578628</v>
+        <v>290.4156971317702</v>
       </c>
       <c r="D6" t="n">
-        <v>69.15234479173684</v>
+        <v>66.21397391292614</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.90609637775757</v>
+        <v>3.054217107911827</v>
       </c>
       <c r="C7" t="n">
-        <v>235.2346039191698</v>
+        <v>190.9185125494687</v>
       </c>
       <c r="D7" t="n">
-        <v>39.94436884268997</v>
+        <v>34.49468733641593</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.507604620824606</v>
+        <v>1.084831213192726</v>
       </c>
       <c r="C8" t="n">
-        <v>148.4549790976814</v>
+        <v>74.85335371029805</v>
       </c>
       <c r="D8" t="n">
-        <v>33.29597338953057</v>
+        <v>26.62008900065226</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>63.01249464937726</v>
+        <v>30.28593492830985</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>20.63437324785945</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>31.03304493124168</v>
+        <v>17.36711688812608</v>
       </c>
       <c r="D10" t="n">
-        <v>24.76949457814703</v>
+        <v>19.92947839621025</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.98900515327081</v>
+        <v>13.14952875068177</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>17.59193711239859</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.35729941108361</v>
+        <v>11.49921085984289</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>13.23494080095125</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.34962535589888</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>8.065057390387548</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.1456838753228</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.99988649347554</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.112721059539136</v>
+        <v>0.1403899217072939</v>
       </c>
       <c r="C2" t="n">
-        <v>3.689407872559513</v>
+        <v>6.927211801165494</v>
       </c>
       <c r="D2" t="n">
-        <v>9.151852098988766</v>
+        <v>11.21646752101981</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.64981916922015</v>
+        <v>1.796598298771663</v>
       </c>
       <c r="C3" t="n">
-        <v>20.86704745376596</v>
+        <v>19.12444527872787</v>
       </c>
       <c r="D3" t="n">
-        <v>69.13958207158161</v>
+        <v>31.66136346195963</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.20859784385261</v>
+        <v>7.376852249710534</v>
       </c>
       <c r="C4" t="n">
-        <v>63.46900733185205</v>
+        <v>81.643120832869</v>
       </c>
       <c r="D4" t="n">
-        <v>158.0407636819473</v>
+        <v>90.70465214306705</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.22897786593033</v>
+        <v>14.67712817848982</v>
       </c>
       <c r="C5" t="n">
-        <v>177.7945092390974</v>
+        <v>194.5087639038994</v>
       </c>
       <c r="D5" t="n">
-        <v>153.0790107846839</v>
+        <v>111.6738013580747</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.89317909334891</v>
+        <v>13.56480802957818</v>
       </c>
       <c r="C6" t="n">
-        <v>288.2421077145678</v>
+        <v>320.8056973167303</v>
       </c>
       <c r="D6" t="n">
-        <v>82.8781594448115</v>
+        <v>81.59010645683969</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.70836417857646</v>
+        <v>6.228207435741766</v>
       </c>
       <c r="C7" t="n">
-        <v>289.3720993221558</v>
+        <v>308.4759278990945</v>
       </c>
       <c r="D7" t="n">
-        <v>45.45393695892307</v>
+        <v>44.13643153982385</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.506221962492859</v>
+        <v>2.002765316663493</v>
       </c>
       <c r="C8" t="n">
-        <v>191.8482276253905</v>
+        <v>160.9722623268283</v>
       </c>
       <c r="D8" t="n">
-        <v>34.29735604786232</v>
+        <v>29.45733986592554</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>0.6656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>73.44061876388687</v>
+        <v>60.68280734719958</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>22.40937309713768</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>31.8871654339364</v>
+        <v>25.90832191507333</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>20.64124548178919</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>16.34806277111788</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>18.12502611580461</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.92336692580652</v>
+        <v>13.0179745583127</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>13.88583952886689</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>8.585383673638358</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.147483139815274</v>
+        <v>0.4427682146153115</v>
       </c>
       <c r="C2" t="n">
-        <v>5.947427592327178</v>
+        <v>18.92220525165302</v>
       </c>
       <c r="D2" t="n">
-        <v>8.033641463851648</v>
+        <v>11.89387343695011</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.02364406035993</v>
+        <v>1.129009859883832</v>
       </c>
       <c r="C3" t="n">
-        <v>17.85799074024948</v>
+        <v>23.12506717353362</v>
       </c>
       <c r="D3" t="n">
-        <v>61.90901022980386</v>
+        <v>32.85418692261951</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.75440850968483</v>
+        <v>5.373105185342793</v>
       </c>
       <c r="C4" t="n">
-        <v>58.24905478837175</v>
+        <v>64.3113468620958</v>
       </c>
       <c r="D4" t="n">
-        <v>156.3560846214598</v>
+        <v>85.70166584222532</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.78719139901926</v>
+        <v>13.2045066221196</v>
       </c>
       <c r="C5" t="n">
-        <v>151.6063892283137</v>
+        <v>172.8121396400448</v>
       </c>
       <c r="D5" t="n">
-        <v>168.6887992822082</v>
+        <v>118.49694790259</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.70829172978102</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="C6" t="n">
-        <v>287.0748096942183</v>
+        <v>313.6811542270112</v>
       </c>
       <c r="D6" t="n">
-        <v>102.8027291025005</v>
+        <v>96.08070257152261</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>29.58398531977338</v>
+        <v>10.59992996275281</v>
       </c>
       <c r="C7" t="n">
-        <v>341.1740169367388</v>
+        <v>384.4121493271768</v>
       </c>
       <c r="D7" t="n">
-        <v>53.65840252331367</v>
+        <v>54.5567016726995</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.595201150680824</v>
+        <v>4.005530633326986</v>
       </c>
       <c r="C8" t="n">
-        <v>268.2036553231861</v>
+        <v>276.7988564738669</v>
       </c>
       <c r="D8" t="n">
-        <v>37.63529824230147</v>
+        <v>33.79666471869644</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>1.220312396378785</v>
       </c>
       <c r="C9" t="n">
-        <v>132.7921762241278</v>
+        <v>123.6953019965768</v>
       </c>
       <c r="D9" t="n">
-        <v>33.50312215512664</v>
+        <v>24.4062479275757</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>50.39310965898878</v>
+        <v>46.26486056263094</v>
       </c>
       <c r="D10" t="n">
-        <v>26.47773558353648</v>
+        <v>21.21065915025234</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.72062817711293</v>
+        <v>22.21204180858408</v>
       </c>
       <c r="D11" t="n">
-        <v>24.87748682561417</v>
+        <v>18.8358114536793</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>15.4046032273367</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>14.53673825678252</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>9.365873098514571</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>7.883434065101886</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.564545987670921</v>
+        <v>2.324778563656447</v>
       </c>
       <c r="C2" t="n">
-        <v>5.867906028283186</v>
+        <v>14.3433339590459</v>
       </c>
       <c r="D2" t="n">
-        <v>7.191301933607885</v>
+        <v>21.46100481483527</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.250165738133689</v>
+        <v>0.585121631731099</v>
       </c>
       <c r="C2" t="n">
-        <v>3.377212102609028</v>
+        <v>19.62906359871073</v>
       </c>
       <c r="D2" t="n">
-        <v>5.912084674974292</v>
+        <v>10.98084807200057</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.41067364001143</v>
+        <v>1.266454538478385</v>
       </c>
       <c r="C3" t="n">
-        <v>22.15313694632928</v>
+        <v>46.80482179996669</v>
       </c>
       <c r="D3" t="n">
-        <v>66.04216806468294</v>
+        <v>34.42007451089317</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.56443248114646</v>
+        <v>3.82881604656256</v>
       </c>
       <c r="C4" t="n">
-        <v>85.03800439415447</v>
+        <v>61.12066682329367</v>
       </c>
       <c r="D4" t="n">
-        <v>160.6443585936098</v>
+        <v>82.23020596000859</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.81491701444964</v>
+        <v>11.16738013580747</v>
       </c>
       <c r="C5" t="n">
-        <v>236.1839539491765</v>
+        <v>146.7958254775043</v>
       </c>
       <c r="D5" t="n">
-        <v>152.1708941582556</v>
+        <v>121.5403657857552</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>18.35475507859837</v>
+        <v>17.06670209062656</v>
       </c>
       <c r="C6" t="n">
-        <v>280.9565580013522</v>
+        <v>298.3452733389718</v>
       </c>
       <c r="D6" t="n">
-        <v>81.10708658635025</v>
+        <v>107.0694046251572</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.689227946110266</v>
+        <v>14.3727863901733</v>
       </c>
       <c r="C7" t="n">
-        <v>188.5829347610656</v>
+        <v>417.2898981946982</v>
       </c>
       <c r="D7" t="n">
-        <v>33.29695513723482</v>
+        <v>66.1148173947972</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.752419652080557</v>
+        <v>6.842781498600267</v>
       </c>
       <c r="C8" t="n">
-        <v>97.88515485192822</v>
+        <v>372.8481431188536</v>
       </c>
       <c r="D8" t="n">
-        <v>24.61732368398877</v>
+        <v>38.46978379091126</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>2.218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>38.38437174064178</v>
+        <v>214.5531067815064</v>
       </c>
       <c r="D9" t="n">
-        <v>20.1906232855399</v>
+        <v>26.73593522975338</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>21.6377194015997</v>
+        <v>85.41205026947252</v>
       </c>
       <c r="D10" t="n">
-        <v>19.50241814486289</v>
+        <v>21.92242623583128</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.81497376771187</v>
+        <v>34.29539255245382</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>19.36890045708532</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>18.87606310955342</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>14.97067074205961</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.626036240139976</v>
+        <v>15.34962535589888</v>
       </c>
       <c r="D13" t="n">
-        <v>9.365873098514571</v>
+        <v>9.886199381765381</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>10.75013736150257</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.085854018625978</v>
+        <v>5.450663253978291</v>
       </c>
       <c r="C2" t="n">
-        <v>7.142214548395546</v>
+        <v>11.57971417159113</v>
       </c>
       <c r="D2" t="n">
-        <v>17.75098024048658</v>
+        <v>23.17219106333746</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.8202423591316</v>
+        <v>3.765002445786518</v>
       </c>
       <c r="C3" t="n">
-        <v>15.0207398749762</v>
+        <v>28.31851252899925</v>
       </c>
       <c r="D3" t="n">
-        <v>9.174432296186444</v>
+        <v>17.58801012158161</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>3.657010198319369</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>8.29576810088555</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>5.675483478250811</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.32958949118645</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.405903770210439</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39880544764168</v>
+        <v>11.6764364414251</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14668734353586</v>
+        <v>59.93904039931552</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576330052663727</v>
+        <v>0.7784290960950068</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.264131190171397</v>
+        <v>2.598686173141307</v>
       </c>
       <c r="C2" t="n">
-        <v>7.700828992111981</v>
+        <v>5.397648877948964</v>
       </c>
       <c r="D2" t="n">
-        <v>21.35792130588936</v>
+        <v>18.73763668325462</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.34748193404114</v>
+        <v>13.27813769993811</v>
       </c>
       <c r="C3" t="n">
-        <v>23.04652735719387</v>
+        <v>39.42698780255191</v>
       </c>
       <c r="D3" t="n">
-        <v>21.8684301120977</v>
+        <v>33.56104526967722</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>13.77097504747001</v>
+        <v>4.7860200582032</v>
       </c>
       <c r="C4" t="n">
-        <v>23.41959148480766</v>
+        <v>45.85645351766426</v>
       </c>
       <c r="D4" t="n">
-        <v>19.87155528165969</v>
+        <v>23.64932044760141</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.129631754689585</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>25.72178985126644</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.474225198880216</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>13.72581465307466</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>30.06798693796707</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>6.767186925373263</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.22360179685679</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.842781498600267</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.72187196672443</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>6.8329640215578</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>44.84132639147307</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44237686945025</v>
+        <v>13.62325439368583</v>
       </c>
       <c r="C21" t="n">
-        <v>86.1522077979856</v>
+        <v>73.72584730700565</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251026709357947</v>
+        <v>1.602735811021862</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.300054944601029</v>
+        <v>2.035162990903638</v>
       </c>
       <c r="C2" t="n">
-        <v>6.953718989180158</v>
+        <v>7.488771487994669</v>
       </c>
       <c r="D2" t="n">
-        <v>24.701753986554</v>
+        <v>19.65557078672539</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.85308200172825</v>
+        <v>10.84340339340602</v>
       </c>
       <c r="C3" t="n">
-        <v>27.24349879284899</v>
+        <v>28.14670668075605</v>
       </c>
       <c r="D3" t="n">
-        <v>33.88011327355743</v>
+        <v>41.18922493167493</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.04045694451915</v>
+        <v>17.07651956766902</v>
       </c>
       <c r="C4" t="n">
-        <v>43.59745205019236</v>
+        <v>77.63562670413351</v>
       </c>
       <c r="D4" t="n">
-        <v>26.36777984066083</v>
+        <v>35.7483791547391</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>12.12458414744811</v>
+        <v>5.006913291658734</v>
       </c>
       <c r="C5" t="n">
-        <v>26.97351817418112</v>
+        <v>52.84257018108458</v>
       </c>
       <c r="D5" t="n">
-        <v>29.59969328304134</v>
+        <v>28.71612034921921</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>4.508185457901354</v>
       </c>
       <c r="C6" t="n">
-        <v>12.11574841810989</v>
+        <v>10.58618549489336</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>31.55729820530948</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>6.94684675525043</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.82246789644735</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>7.42692138262712</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>23.699389580518</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>34.29735604786232</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>23.96249796525614</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>36.27655941962388</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>7.260024272905163</v>
       </c>
       <c r="C10" t="n">
-        <v>29.46715734296802</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.4142661401257</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.77947628610551</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>41.44055234396211</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73625141340154</v>
+        <v>14.82722091735397</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0911336217494</v>
+        <v>87.31585651330674</v>
       </c>
       <c r="D21" t="n">
-        <v>5.020875424020461</v>
+        <v>2.471203486225662</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.314781160164732</v>
+        <v>1.566869335977909</v>
       </c>
       <c r="C2" t="n">
-        <v>6.068182559949535</v>
+        <v>7.411213419359171</v>
       </c>
       <c r="D2" t="n">
-        <v>26.9921713805618</v>
+        <v>17.03430441638641</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.1448409963388</v>
+        <v>8.69828465962674</v>
       </c>
       <c r="C3" t="n">
-        <v>27.08151042164826</v>
+        <v>28.72102908774044</v>
       </c>
       <c r="D3" t="n">
-        <v>45.11621574866217</v>
+        <v>47.3546005143449</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.31146036862027</v>
+        <v>19.47591095684822</v>
       </c>
       <c r="C4" t="n">
-        <v>57.33013893719674</v>
+        <v>73.53879353431158</v>
       </c>
       <c r="D4" t="n">
-        <v>36.82044764777662</v>
+        <v>48.35794666808514</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.71549845441346</v>
+        <v>15.6834195753428</v>
       </c>
       <c r="C5" t="n">
-        <v>55.61600744558182</v>
+        <v>103.0835089459151</v>
       </c>
       <c r="D5" t="n">
-        <v>32.05406254365837</v>
+        <v>35.12202411942965</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.27046364475338</v>
+        <v>5.715735134124931</v>
       </c>
       <c r="C6" t="n">
-        <v>28.29691407950582</v>
+        <v>50.59633143376788</v>
       </c>
       <c r="D6" t="n">
-        <v>38.15856976866503</v>
+        <v>33.48937768726721</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>17.66654993792135</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>31.54355373745002</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>35.46563581591602</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>7.765624340592267</v>
       </c>
       <c r="C9" t="n">
-        <v>34.39062207976576</v>
+        <v>27.5124976638126</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>37.38593432542277</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.10709261522091</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.27191272300992</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>6.930157044278233</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>28.25371718051895</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.31256528951153</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>42.95931604243193</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>28.09761929554372</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.62610266006477</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.42141611149592</v>
+        <v>26.11939767148639</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.06175181081399</v>
+        <v>16.05957689707648</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8314284800722</v>
+        <v>100.5836658290579</v>
       </c>
       <c r="D21" t="n">
-        <v>6.880667356500569</v>
+        <v>3.380963557279259</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.991205328390784</v>
+        <v>1.315541923690726</v>
       </c>
       <c r="C2" t="n">
-        <v>7.045021525675111</v>
+        <v>10.05211474378309</v>
       </c>
       <c r="D2" t="n">
-        <v>32.24353985057799</v>
+        <v>15.03055735201867</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.6806542586793</v>
+        <v>6.882051406770142</v>
       </c>
       <c r="C3" t="n">
-        <v>23.54721868635975</v>
+        <v>28.71121161069797</v>
       </c>
       <c r="D3" t="n">
-        <v>52.30260894374882</v>
+        <v>49.76479112827082</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.29647211114931</v>
+        <v>18.14858806070654</v>
       </c>
       <c r="C4" t="n">
-        <v>52.86318688287376</v>
+        <v>72.60711496298136</v>
       </c>
       <c r="D4" t="n">
-        <v>43.9675709346934</v>
+        <v>60.52081897599888</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>21.69662426385451</v>
+        <v>22.2856728864026</v>
       </c>
       <c r="C5" t="n">
-        <v>60.96653243372694</v>
+        <v>120.4358996184775</v>
       </c>
       <c r="D5" t="n">
-        <v>30.33600406122645</v>
+        <v>44.03138453546945</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.15600007398401</v>
+        <v>13.32329809433347</v>
       </c>
       <c r="C6" t="n">
-        <v>40.41266249761571</v>
+        <v>107.5524244956466</v>
       </c>
       <c r="D6" t="n">
-        <v>30.91327171132357</v>
+        <v>36.6290068454485</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.509568116233099</v>
+        <v>6.767186925373263</v>
       </c>
       <c r="C7" t="n">
-        <v>19.94224111636546</v>
+        <v>45.87314322863646</v>
       </c>
       <c r="D7" t="n">
-        <v>30.72183090899544</v>
+        <v>37.06981156465531</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.760715602071035</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>25.11801501315464</v>
       </c>
       <c r="D8" t="n">
-        <v>30.37527396939631</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.209374302911826</v>
       </c>
       <c r="C9" t="n">
-        <v>22.07656062539802</v>
+        <v>30.39687241888974</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>38.49530923122167</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>7.829437941368314</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>30.7483380970101</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>44.27191272300992</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.285549713215578</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>30.38607319414302</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>45.66795795844887</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>31.24313893995049</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>44.04414725562465</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>30.69925071179776</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>42.40659208494097</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>28.5776939229204</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>26.87534340375643</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.058844473218861</v>
+        <v>17.31466088092658</v>
       </c>
       <c r="C21" t="n">
-        <v>66.17666693642681</v>
+        <v>114.2767618141154</v>
       </c>
       <c r="D21" t="n">
-        <v>5.294133354914146</v>
+        <v>4.328665220231645</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.946044933995431</v>
+        <v>1.786780821729195</v>
       </c>
       <c r="C2" t="n">
-        <v>8.294786353181301</v>
+        <v>9.204866475018093</v>
       </c>
       <c r="D2" t="n">
-        <v>27.89047052994763</v>
+        <v>17.06179335210532</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.05648370295658</v>
+        <v>5.600870652728053</v>
       </c>
       <c r="C3" t="n">
-        <v>26.11448893296516</v>
+        <v>34.00774047510951</v>
       </c>
       <c r="D3" t="n">
-        <v>66.74902641174064</v>
+        <v>49.87278337573797</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.35952494839936</v>
+        <v>15.67262035059608</v>
       </c>
       <c r="C4" t="n">
-        <v>56.80686741083319</v>
+        <v>71.39465654823654</v>
       </c>
       <c r="D4" t="n">
-        <v>60.75054793879262</v>
+        <v>69.32709588309277</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.83883881225006</v>
+        <v>24.54369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>83.52218593879741</v>
+        <v>127.136327699962</v>
       </c>
       <c r="D5" t="n">
-        <v>40.32528695193774</v>
+        <v>54.48699758569799</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>21.93715245139498</v>
+        <v>21.1321193339126</v>
       </c>
       <c r="C6" t="n">
-        <v>73.258013690897</v>
+        <v>147.9248353373882</v>
       </c>
       <c r="D6" t="n">
-        <v>34.05290086950487</v>
+        <v>41.21769561509809</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.71970318267092</v>
+        <v>10.89936301254809</v>
       </c>
       <c r="C7" t="n">
-        <v>42.75903951076558</v>
+        <v>96.83664830379264</v>
       </c>
       <c r="D7" t="n">
-        <v>32.93763547748049</v>
+        <v>39.40538935305847</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>7.760715602071035</v>
       </c>
       <c r="C8" t="n">
-        <v>23.61594102565702</v>
+        <v>42.14152020479433</v>
       </c>
       <c r="D8" t="n">
-        <v>32.3780392860598</v>
+        <v>38.21943812632832</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>8.431249284071605</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>31.61718481526852</v>
       </c>
       <c r="D9" t="n">
-        <v>31.17343485294896</v>
+        <v>39.60468413702056</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>8.114144775599888</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>33.73775985644164</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>44.4142661401257</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>33.40691088011046</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>45.84565429291754</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.292021036517808</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>33.1958351236974</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>44.91201222617883</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>32.5203927031756</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>42.66675522656638</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>31.03599017435442</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>28.66703296400686</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>41.20885988575986</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.28081560192251</v>
+        <v>17.70100700204667</v>
       </c>
       <c r="C21" t="n">
-        <v>75.53846186994605</v>
+        <v>126.5622000646336</v>
       </c>
       <c r="D21" t="n">
-        <v>6.370713651682196</v>
+        <v>5.310302100613999</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.039891802975625</v>
+        <v>1.619883712007237</v>
       </c>
       <c r="C2" t="n">
-        <v>8.300676839406782</v>
+        <v>5.816855147662351</v>
       </c>
       <c r="D2" t="n">
-        <v>27.32498385230147</v>
+        <v>13.56775327269092</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.67007601811084</v>
+        <v>8.948630324209677</v>
       </c>
       <c r="C3" t="n">
-        <v>29.85003894762427</v>
+        <v>49.86787463721674</v>
       </c>
       <c r="D3" t="n">
-        <v>73.57217295625597</v>
+        <v>55.96452788058943</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.8692729910817</v>
+        <v>11.79275342341269</v>
       </c>
       <c r="C4" t="n">
-        <v>61.89919275276139</v>
+        <v>107.3217137851486</v>
       </c>
       <c r="D4" t="n">
-        <v>80.55828961967627</v>
+        <v>65.62590703808229</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.89483948912113</v>
+        <v>11.90369091399258</v>
       </c>
       <c r="C5" t="n">
-        <v>95.84311962709488</v>
+        <v>88.38183707481912</v>
       </c>
       <c r="D5" t="n">
-        <v>52.64622064023522</v>
+        <v>40.30074325933157</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.43654323768712</v>
+        <v>6.762278186852032</v>
       </c>
       <c r="C6" t="n">
-        <v>105.33858342257</v>
+        <v>63.75862290460487</v>
       </c>
       <c r="D6" t="n">
-        <v>39.40637110076273</v>
+        <v>25.92206638293279</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.86428213710246</v>
+        <v>5.090361846519712</v>
       </c>
       <c r="C7" t="n">
-        <v>77.792706336813</v>
+        <v>29.58398531977338</v>
       </c>
       <c r="D7" t="n">
-        <v>35.39298648580176</v>
+        <v>26.82920126165683</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.012443924985718</v>
+        <v>5.841398840268521</v>
       </c>
       <c r="C8" t="n">
-        <v>41.8911745402114</v>
+        <v>23.28214680621311</v>
       </c>
       <c r="D8" t="n">
-        <v>34.38080460272329</v>
+        <v>29.12354564648163</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>27.29062268265283</v>
+        <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>33.83593462686631</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>26.90479583488384</v>
+        <v>26.1930287493049</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>35.87306111317846</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>26.4698816019025</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>34.60169783617884</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>23.96838845148163</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>34.41614752007619</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>32.25041208450772</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>30.17205219461722</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>30.69237847786803</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>13.23984953947248</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>13.4499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>96.16709636949629</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.490113827687003</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>84.26378056147878</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.490113827687003</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
